--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO3" headerRowCount="1">
+  <autoFilter ref="A1:CO3"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$3)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$3,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")/(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$3)/SUM('Picks'!$BX$2:$BX$3),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$3)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$3,"&lt;&gt;",'Picks'!$AB$2:$AB$3),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$3,'Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,547 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>a896c47e709542e0</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:19.923501Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>62513</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.643378</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.09382799999999999</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n"/>
+      <c r="X2" s="26" t="n"/>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:19.057098Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-bald-kw-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:14.567529Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>35348cc31f974406</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:11.100365Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>62515</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.523841</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>0.054357</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="26" t="n"/>
+      <c r="X3" s="26" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Team Bald</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:06.898700Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -1853,12 +1853,12 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>35348cc31f974406</t>
+          <t>951623d4fee64f5a</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:11.100365Z</t>
+          <t>2026-07-28T11:18:10.759539Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
@@ -1903,23 +1903,23 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.5</v>
       </c>
       <c r="O3" s="28" t="n">
         <v>0.523841</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>0.054357</v>
+        <v>0.023841</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="S3" s="29" t="n">
         <v>0.75</v>
@@ -1945,7 +1945,7 @@
       <c r="AD3" s="24" t="n"/>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>18a9ff14f2d62153ff8f669de0259e5da8a942e12ddd5bbf4dcc409861b4617b</t>
+          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:06.898700Z</t>
+          <t>2026-07-28T11:18:04.530689Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2074,13 +2074,13 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO3" headerRowCount="1">
-  <autoFilter ref="A1:CO3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
+  <autoFilter ref="A1:CO13"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$3)</f>
+        <f>COUNTA('Picks'!$A$2:$A$13)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$3,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$3,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")/(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$3)/SUM('Picks'!$BX$2:$BX$3),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$3)</f>
+        <f>SUM('Picks'!$BY$2:$BY$13)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$3,"&lt;&gt;",'Picks'!$AB$2:$AB$3),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$3,'Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO3"/>
+  <dimension ref="A1:CO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1931,18 +1931,28 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W3" s="26" t="n"/>
       <c r="X3" s="26" t="n"/>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:31.201568Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
@@ -2091,7 +2101,11 @@
       <c r="BT3" s="28" t="n"/>
       <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
-      <c r="BW3" s="24" t="n"/>
+      <c r="BW3" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX3" s="30" t="n"/>
       <c r="BY3" s="27" t="n"/>
       <c r="BZ3" s="24" t="n"/>
@@ -2111,6 +2125,2672 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
     </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>675cfea603ef49ca</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:23.509787Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>62517</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.639298</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>0.108782</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n"/>
+      <c r="X4" s="26" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:34:50.765009Z</t>
+        </is>
+      </c>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-agm-tje-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Team Jenz</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:30:19.772763Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>34dc8a8e407b4e13</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:57:41.131320Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>62625</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.545326</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.035522</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:05:08.365028Z</t>
+        </is>
+      </c>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-rae-z10-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:57:35.327439Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>bf169b35b9b8478a</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:11.833269Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>62691</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.783842</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:13:07.864236Z</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-dota2-agm-nemiga-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Amaru Gaming</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:07.620398Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>62e6c3c7b23b45ba</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:30:19.883158Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>63691</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.574553</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>0.124103</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:01:12.820826Z</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-z10-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:30:13.979212Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>19a3c157d0b145d6</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>64671</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.747717</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.127945</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-re-midas-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Midas Club</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:06.676111Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>36b183817611490c</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>64672</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.598287</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.048737</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-yes-xctn-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:07.226095Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>7e84c1d1488b42b3</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>64735</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.6120679999999999</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.021904</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-tr-pla-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:07.804702Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>6183f78884904843</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>64818</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.605405</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.144576</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Enjoy</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:09.456160Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>05e3b1e509154dd1</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>64928</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.70634</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.07671</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.047707Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>9dfaf074bb4749c9</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.595951Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>64929</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.611965</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.262315</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:10.594126Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3228,12 +3228,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>19a3c157d0b145d6</t>
+          <t>0e703c057fc24630</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:06.676111Z</t>
+          <t>2026-07-30T17:22:15.485981Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3489,12 +3489,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>36b183817611490c</t>
+          <t>55d41d60131849b7</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:07.226095Z</t>
+          <t>2026-07-30T17:22:16.072763Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3750,12 +3750,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>7e84c1d1488b42b3</t>
+          <t>d91ff5e85dfc4aa8</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:07.804702Z</t>
+          <t>2026-07-30T17:22:16.574192Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>6183f78884904843</t>
+          <t>ad374a89479a45b2</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:09.456160Z</t>
+          <t>2026-07-30T17:22:18.197240Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>05e3b1e509154dd1</t>
+          <t>0365715ac9b44d5e</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.047707Z</t>
+          <t>2026-07-30T17:22:18.719201Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4533,12 +4533,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>9dfaf074bb4749c9</t>
+          <t>00053d56ee6d45ec</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.595951Z</t>
+          <t>2026-07-30T17:22:19.251723Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>e26af3cd0f446cfff3c995c2e8ad9ebb3019f15f33af3fcadfb25b344b7aa502</t>
+          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:10.594126Z</t>
+          <t>2026-07-30T17:22:19.250107Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3228,12 +3228,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>0e703c057fc24630</t>
+          <t>b50087ea130643e5</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:15.485981Z</t>
+          <t>2026-07-30T17:39:52.434355Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3489,12 +3489,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>55d41d60131849b7</t>
+          <t>6595f067e3cb43a2</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:16.072763Z</t>
+          <t>2026-07-30T17:39:52.965080Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3750,12 +3750,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>d91ff5e85dfc4aa8</t>
+          <t>024bef67d3da4530</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:16.574192Z</t>
+          <t>2026-07-30T17:39:53.524510Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>ad374a89479a45b2</t>
+          <t>d42579b5f4c04fd9</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:18.197240Z</t>
+          <t>2026-07-30T17:39:55.261695Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>0365715ac9b44d5e</t>
+          <t>e3835d2a50b14f5a</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:18.719201Z</t>
+          <t>2026-07-30T17:39:55.839894Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4533,12 +4533,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>00053d56ee6d45ec</t>
+          <t>cf0fded42cca479e</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.251723Z</t>
+          <t>2026-07-30T17:39:56.381240Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>4980c426b69846ac083c0548b60f7e06fe2d485cb9671bb10a6ae7ef9a2d16a0</t>
+          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:19.250107Z</t>
+          <t>2026-07-30T17:39:56.380308Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
-  <autoFilter ref="A1:CO13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO7" headerRowCount="1">
+  <autoFilter ref="A1:CO7"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$13)</f>
+        <f>COUNTA('Picks'!$A$2:$A$7)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$13)</f>
+        <f>SUM('Picks'!$BY$2:$BY$7)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO13"/>
+  <dimension ref="A1:CO7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1578,22 +1578,22 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>a896c47e709542e0</t>
+          <t>e5513af8c76d4b03</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:38:19.923501Z</t>
+          <t>2026-07-31T10:46:51.141594Z</t>
         </is>
       </c>
       <c r="C2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T18:00:00Z</t>
+          <t>2026-07-31T11:00:00Z</t>
         </is>
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
-          <t>62513</t>
+          <t>64818</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I2" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J2" s="25" t="n"/>
@@ -1628,30 +1628,30 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>-122</v>
+        <v>117</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.460829</v>
       </c>
       <c r="O2" s="28" t="n">
-        <v>0.643378</v>
+        <v>0.675115</v>
       </c>
       <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
-        <v>0.09382799999999999</v>
+        <v>0.214286</v>
       </c>
       <c r="R2" s="26" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="S2" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U2" s="24" t="inlineStr">
@@ -1661,26 +1661,36 @@
       </c>
       <c r="V2" s="24" t="inlineStr">
         <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
-      <c r="Z2" s="26" t="n"/>
-      <c r="AA2" s="28" t="n"/>
-      <c r="AB2" s="28" t="n"/>
+      <c r="Z2" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
       <c r="AC2" s="30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:57:19.057098Z</t>
+          <t>2026-07-31T16:45:02.553574Z</t>
         </is>
       </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-bald-kw-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
         </is>
       </c>
       <c r="AF2" s="31" t="inlineStr">
@@ -1721,32 +1731,32 @@
       </c>
       <c r="AP2" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AQ2" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AR2" s="24" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>GLYPH</t>
         </is>
       </c>
       <c r="AS2" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AT2" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AU2" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Enjoy</t>
         </is>
       </c>
       <c r="AV2" s="24" t="n"/>
@@ -1764,7 +1774,7 @@
       </c>
       <c r="BA2" s="24" t="inlineStr">
         <is>
-          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
         </is>
       </c>
       <c r="BB2" s="24" t="inlineStr">
@@ -1774,12 +1784,12 @@
       </c>
       <c r="BC2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD2" s="24" t="inlineStr">
         <is>
-          <t>713355eeac1c7f851a8fe35e939969377fe0747dd60b1ddb9f28fd4faae96635</t>
+          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
         </is>
       </c>
       <c r="BE2" s="24" t="inlineStr">
@@ -1794,12 +1804,12 @@
       </c>
       <c r="BG2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:38:14.567529Z</t>
+          <t>2026-07-31T10:46:49.443966Z</t>
         </is>
       </c>
       <c r="BI2" s="24" t="inlineStr">
@@ -1809,28 +1819,28 @@
       </c>
       <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
-        <v>-122</v>
+        <v>117</v>
       </c>
       <c r="BL2" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.460829</v>
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
       <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
-      <c r="BR2" s="28" t="n"/>
+      <c r="BQ2" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR2" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
       <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
-      <c r="BW2" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW2" s="24" t="n"/>
       <c r="BX2" s="30" t="n"/>
       <c r="BY2" s="27" t="n"/>
       <c r="BZ2" s="24" t="n"/>
@@ -1853,22 +1863,22 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>951623d4fee64f5a</t>
+          <t>720d6ff896f64777</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:10.759539Z</t>
+          <t>2026-07-31T13:44:01.315844Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T12:00:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>64929</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -1878,12 +1888,12 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -1903,30 +1913,30 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.5</v>
+        <v>0.390625</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.523841</v>
+        <v>0.610359</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>0.023841</v>
+        <v>0.219734</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="S3" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1936,26 +1946,36 @@
       </c>
       <c r="V3" s="24" t="inlineStr">
         <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
+      <c r="Z3" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
       <c r="AC3" s="30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T20:31:31.201568Z</t>
+          <t>2026-07-31T19:51:28.507069Z</t>
         </is>
       </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-bald-lvlup-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -1996,32 +2016,32 @@
       </c>
       <c r="AP3" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AR3" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AS3" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT3" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU3" s="24" t="inlineStr">
         <is>
-          <t>Team Bald</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV3" s="24" t="n"/>
@@ -2039,7 +2059,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2049,12 +2069,12 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>2eec6caa3ac9ef66f075873fd68ca2373e4c3dc3d989a802f3e79917f2c19f1e</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2069,12 +2089,12 @@
       </c>
       <c r="BG3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:18:04.530689Z</t>
+          <t>2026-07-31T13:43:57.933952Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2084,28 +2104,28 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.5</v>
+        <v>0.390625</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
-      <c r="BR3" s="28" t="n"/>
+      <c r="BQ3" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR3" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
       <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
-      <c r="BW3" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW3" s="24" t="n"/>
       <c r="BX3" s="30" t="n"/>
       <c r="BY3" s="27" t="n"/>
       <c r="BZ3" s="24" t="n"/>
@@ -2128,22 +2148,22 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>675cfea603ef49ca</t>
+          <t>0938e25298a64dae</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:23.509787Z</t>
+          <t>2026-07-31T13:44:01.315844Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T18:00:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>62517</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2153,12 +2173,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2168,7 +2188,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J4" s="25" t="n"/>
@@ -2178,30 +2198,30 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>-113</v>
+        <v>-127</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.787402</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.639298</v>
+        <v>0.701925</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>0.108782</v>
+        <v>0.142454</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="S4" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2211,26 +2231,36 @@
       </c>
       <c r="V4" s="24" t="inlineStr">
         <is>
-          <t>push</t>
-        </is>
-      </c>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="26" t="n"/>
-      <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n"/>
+      <c r="Z4" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.000529</v>
+      </c>
       <c r="AC4" s="30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T17:34:50.765009Z</t>
+          <t>2026-07-31T23:28:46.755247Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-agm-tje-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2240,7 +2270,7 @@
       </c>
       <c r="AG4" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH4" s="24" t="n"/>
@@ -2271,32 +2301,32 @@
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>Team Jenz</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2314,7 +2344,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2324,12 +2354,12 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>d5654d4f52e87448d68cdf73205dec099fa0dc5a5637072a26a63fb8afd8476d</t>
+          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2344,12 +2374,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:30:19.772763Z</t>
+          <t>2026-07-31T13:43:58.701955Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2359,28 +2389,28 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>-113</v>
+        <v>-127</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.787402</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
       <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
-      <c r="BR4" s="28" t="n"/>
+      <c r="BQ4" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR4" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
       <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
-      <c r="BW4" s="24" t="inlineStr">
-        <is>
-          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
-        </is>
-      </c>
+      <c r="BW4" s="24" t="n"/>
       <c r="BX4" s="30" t="n"/>
       <c r="BY4" s="27" t="n"/>
       <c r="BZ4" s="24" t="n"/>
@@ -2403,22 +2433,22 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>34dc8a8e407b4e13</t>
+          <t>631326b56379473e</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T08:57:41.131320Z</t>
+          <t>2026-08-01T03:02:50.460010Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T12:00:00Z</t>
+          <t>2026-08-01T05:00:00Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>62625</t>
+          <t>67530</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2428,12 +2458,12 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2443,7 +2473,7 @@
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J5" s="25" t="n"/>
@@ -2453,30 +2483,30 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>-104</v>
+        <v>-150</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.666667</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.6</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.545326</v>
+        <v>0.630791</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.035522</v>
+        <v>0.030791</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S5" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2486,7 +2516,7 @@
       </c>
       <c r="V5" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W5" s="26" t="n">
@@ -2500,16 +2530,16 @@
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T15:05:08.365028Z</t>
+          <t>2026-08-01T10:16:06.748137Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-rae-z10-2026-07-29).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-midas-tr-2026-08-01).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2519,7 +2549,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2550,32 +2580,32 @@
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Midas Club</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
+          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2603,12 +2633,12 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>ea4069f9fa26716d37364f94a04d40c374520e264563d131060f068b82243fc0</t>
+          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2623,12 +2653,12 @@
       </c>
       <c r="BG5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T08:57:35.327439Z</t>
+          <t>2026-08-01T03:02:45.273136Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2638,13 +2668,13 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>-104</v>
+        <v>-150</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.666667</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
@@ -2678,22 +2708,22 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>bf169b35b9b8478a</t>
+          <t>9518099e84cd4bb6</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T12:04:11.833269Z</t>
+          <t>2026-08-01T06:42:17.908342Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T15:00:00Z</t>
+          <t>2026-08-01T08:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>62691</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2703,12 +2733,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2718,7 +2748,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J6" s="25" t="n"/>
@@ -2728,30 +2758,30 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>178</v>
+        <v>-178</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>2.78</v>
+        <v>1.561798</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.640288</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.783842</v>
+        <v>0.685333</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.42413</v>
+        <v>0.045045</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2765,26 +2795,32 @@
         </is>
       </c>
       <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="X6" s="26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
+      <c r="Z6" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>-0.000288</v>
+      </c>
       <c r="AC6" s="30" t="n">
         <v>-2</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T04:13:07.864236Z</t>
+          <t>2026-08-01T13:41:26.204467Z</t>
         </is>
       </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-dota2-agm-nemiga-2026-07-29).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-re-pla-2026-08-01).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2825,32 +2861,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>Nemiga Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>Amaru Gaming</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2868,7 +2904,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2878,12 +2914,12 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>1975149062e5ce6b992f64d64cd516228ceab5b0d4760dfd8a040fce4af22aeb</t>
+          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2898,12 +2934,12 @@
       </c>
       <c r="BG6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-29T12:04:07.620398Z</t>
+          <t>2026-08-01T06:42:13.849047Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2913,19 +2949,23 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>178</v>
+        <v>-178</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>2.78</v>
+        <v>1.561798</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.640288</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
+      <c r="BQ6" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR6" s="28" t="n">
+        <v>0.64</v>
+      </c>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
       <c r="BU6" s="25" t="n"/>
@@ -2953,22 +2993,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>62e6c3c7b23b45ba</t>
+          <t>3e91bccc1332447f</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T10:30:19.883158Z</t>
+          <t>2026-08-01T21:24:30.033213Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T12:00:00Z</t>
+          <t>2026-08-02T08:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>63691</t>
+          <t>68446</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2978,12 +3018,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -2993,7 +3033,7 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -3003,63 +3043,49 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.22</v>
+        <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.509804</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.574553</v>
+        <v>0.576057</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.124103</v>
+        <v>0.06625300000000001</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W7" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="26" t="n">
-        <v>1</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AD7" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:01:12.820826Z</t>
-        </is>
-      </c>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-z10-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3069,7 +3095,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3100,32 +3126,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3143,7 +3169,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3153,12 +3179,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>3bcd1fbb498942b21a2e085eda89faf5557d0f6661ee26a8410d8dba9769a397</t>
+          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3173,12 +3199,12 @@
       </c>
       <c r="BG7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v4</t>
+          <t>dota2-tiered-elo-v5</t>
         </is>
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T10:30:13.979212Z</t>
+          <t>2026-08-01T21:24:29.070923Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3188,13 +3214,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.22</v>
+        <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.509804</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3225,1572 +3251,6 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>b50087ea130643e5</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>64671</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N8" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O8" s="28" t="n">
-        <v>0.747717</v>
-      </c>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n">
-        <v>0.127945</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S8" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U8" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
-      <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-re-midas-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH8" s="24" t="n"/>
-      <c r="AI8" s="31" t="n"/>
-      <c r="AJ8" s="31" t="n"/>
-      <c r="AK8" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL8" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN8" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP8" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="AQ8" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="AR8" s="24" t="inlineStr">
-        <is>
-          <t>Midas Club</t>
-        </is>
-      </c>
-      <c r="AS8" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AT8" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AU8" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AV8" s="24" t="n"/>
-      <c r="AW8" s="24" t="n"/>
-      <c r="AX8" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY8" s="24" t="n"/>
-      <c r="AZ8" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA8" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB8" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC8" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD8" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG8" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:52.434355Z</t>
-        </is>
-      </c>
-      <c r="BI8" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ8" s="25" t="n"/>
-      <c r="BK8" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL8" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM8" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN8" s="28" t="n"/>
-      <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
-      <c r="BS8" s="28" t="n"/>
-      <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
-      <c r="BV8" s="29" t="n"/>
-      <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
-      <c r="BZ8" s="24" t="n"/>
-      <c r="CA8" s="31" t="n"/>
-      <c r="CB8" s="24" t="n"/>
-      <c r="CC8" s="24" t="n"/>
-      <c r="CD8" s="24" t="n"/>
-      <c r="CE8" s="24" t="n"/>
-      <c r="CF8" s="24" t="n"/>
-      <c r="CG8" s="24" t="n"/>
-      <c r="CH8" s="24" t="n"/>
-      <c r="CI8" s="24" t="n"/>
-      <c r="CJ8" s="24" t="n"/>
-      <c r="CK8" s="24" t="n"/>
-      <c r="CL8" s="24" t="n"/>
-      <c r="CM8" s="24" t="n"/>
-      <c r="CN8" s="24" t="n"/>
-      <c r="CO8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>6595f067e3cb43a2</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>64672</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.598287</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.048737</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-yes-xctn-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>Execration</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:52.965080Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN9" s="28" t="n"/>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
-      <c r="CB9" s="24" t="n"/>
-      <c r="CC9" s="24" t="n"/>
-      <c r="CD9" s="24" t="n"/>
-      <c r="CE9" s="24" t="n"/>
-      <c r="CF9" s="24" t="n"/>
-      <c r="CG9" s="24" t="n"/>
-      <c r="CH9" s="24" t="n"/>
-      <c r="CI9" s="24" t="n"/>
-      <c r="CJ9" s="24" t="n"/>
-      <c r="CK9" s="24" t="n"/>
-      <c r="CL9" s="24" t="n"/>
-      <c r="CM9" s="24" t="n"/>
-      <c r="CN9" s="24" t="n"/>
-      <c r="CO9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>024bef67d3da4530</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>64735</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.6120679999999999</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>0.021904</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-tr-pla-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>Team Resilience</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:53.524510Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN10" s="28" t="n"/>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
-      <c r="CB10" s="24" t="n"/>
-      <c r="CC10" s="24" t="n"/>
-      <c r="CD10" s="24" t="n"/>
-      <c r="CE10" s="24" t="n"/>
-      <c r="CF10" s="24" t="n"/>
-      <c r="CG10" s="24" t="n"/>
-      <c r="CH10" s="24" t="n"/>
-      <c r="CI10" s="24" t="n"/>
-      <c r="CJ10" s="24" t="n"/>
-      <c r="CK10" s="24" t="n"/>
-      <c r="CL10" s="24" t="n"/>
-      <c r="CM10" s="24" t="n"/>
-      <c r="CN10" s="24" t="n"/>
-      <c r="CO10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>d42579b5f4c04fd9</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>64818</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.605405</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.144576</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>92</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>Enjoy</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:55.261695Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN11" s="28" t="n"/>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-      <c r="CB11" s="24" t="n"/>
-      <c r="CC11" s="24" t="n"/>
-      <c r="CD11" s="24" t="n"/>
-      <c r="CE11" s="24" t="n"/>
-      <c r="CF11" s="24" t="n"/>
-      <c r="CG11" s="24" t="n"/>
-      <c r="CH11" s="24" t="n"/>
-      <c r="CI11" s="24" t="n"/>
-      <c r="CJ11" s="24" t="n"/>
-      <c r="CK11" s="24" t="n"/>
-      <c r="CL11" s="24" t="n"/>
-      <c r="CM11" s="24" t="n"/>
-      <c r="CN11" s="24" t="n"/>
-      <c r="CO11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>e3835d2a50b14f5a</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>64928</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0.70634</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>0.07671</v>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>58</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH12" s="24" t="n"/>
-      <c r="AI12" s="31" t="n"/>
-      <c r="AJ12" s="31" t="n"/>
-      <c r="AK12" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL12" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM12" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN12" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO12" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP12" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AQ12" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AR12" s="24" t="inlineStr">
-        <is>
-          <t>LGD Gaming</t>
-        </is>
-      </c>
-      <c r="AS12" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AT12" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AU12" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AV12" s="24" t="n"/>
-      <c r="AW12" s="24" t="n"/>
-      <c r="AX12" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY12" s="24" t="n"/>
-      <c r="AZ12" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA12" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB12" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC12" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:55.839894Z</t>
-        </is>
-      </c>
-      <c r="BI12" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ12" s="25" t="n"/>
-      <c r="BK12" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL12" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM12" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN12" s="28" t="n"/>
-      <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
-      <c r="BS12" s="28" t="n"/>
-      <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
-      <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
-      <c r="BZ12" s="24" t="n"/>
-      <c r="CA12" s="31" t="n"/>
-      <c r="CB12" s="24" t="n"/>
-      <c r="CC12" s="24" t="n"/>
-      <c r="CD12" s="24" t="n"/>
-      <c r="CE12" s="24" t="n"/>
-      <c r="CF12" s="24" t="n"/>
-      <c r="CG12" s="24" t="n"/>
-      <c r="CH12" s="24" t="n"/>
-      <c r="CI12" s="24" t="n"/>
-      <c r="CJ12" s="24" t="n"/>
-      <c r="CK12" s="24" t="n"/>
-      <c r="CL12" s="24" t="n"/>
-      <c r="CM12" s="24" t="n"/>
-      <c r="CN12" s="24" t="n"/>
-      <c r="CO12" s="24" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>cf0fded42cca479e</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.381240Z</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>64929</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0.611965</v>
-      </c>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n">
-        <v>0.262315</v>
-      </c>
-      <c r="R13" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S13" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG13" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH13" s="24" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN13" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO13" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP13" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AQ13" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AR13" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AS13" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AT13" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AU13" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AV13" s="24" t="n"/>
-      <c r="AW13" s="24" t="n"/>
-      <c r="AX13" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY13" s="24" t="n"/>
-      <c r="AZ13" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA13" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BB13" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC13" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>a2f59131fded62add8d43e12024c13e5f1c6411a2f723e73a857cdf6849678a3</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T17:39:56.380308Z</t>
-        </is>
-      </c>
-      <c r="BI13" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ13" s="25" t="n"/>
-      <c r="BK13" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="BL13" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BM13" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="BN13" s="28" t="n"/>
-      <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
-      <c r="BS13" s="28" t="n"/>
-      <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
-      <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
-      <c r="BZ13" s="24" t="n"/>
-      <c r="CA13" s="31" t="n"/>
-      <c r="CB13" s="24" t="n"/>
-      <c r="CC13" s="24" t="n"/>
-      <c r="CD13" s="24" t="n"/>
-      <c r="CE13" s="24" t="n"/>
-      <c r="CF13" s="24" t="n"/>
-      <c r="CG13" s="24" t="n"/>
-      <c r="CH13" s="24" t="n"/>
-      <c r="CI13" s="24" t="n"/>
-      <c r="CJ13" s="24" t="n"/>
-      <c r="CK13" s="24" t="n"/>
-      <c r="CL13" s="24" t="n"/>
-      <c r="CM13" s="24" t="n"/>
-      <c r="CN13" s="24" t="n"/>
-      <c r="CO13" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO7" headerRowCount="1">
-  <autoFilter ref="A1:CO7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
+  <autoFilter ref="A1:CO8"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$7)</f>
+        <f>COUNTA('Picks'!$A$2:$A$8)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$7)</f>
+        <f>SUM('Picks'!$BY$2:$BY$8)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO7"/>
+  <dimension ref="A1:CO8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2993,12 +2993,12 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>3e91bccc1332447f</t>
+          <t>ed3b2bbfc78f4fd7</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:30.033213Z</t>
+          <t>2026-08-02T07:16:32.312595Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -3043,23 +3043,23 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-104</v>
+        <v>127</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.27</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.440529</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.576057</v>
+        <v>0.576085</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.06625300000000001</v>
+        <v>0.135556</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1.25</v>
@@ -3085,7 +3085,7 @@
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>65b8f79741d3dcd1d060bb1f14ea0523262331890046cd8c8cccbede889da72c</t>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:29.070923Z</t>
+          <t>2026-08-02T07:16:30.813424Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3214,13 +3214,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-104</v>
+        <v>127</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.27</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.440529</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3251,6 +3251,267 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
     </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>ccb0db69fd82419f</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:32.312595Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>69232</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.702765</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.212569</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>REKONIX</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:31.369505Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3254,12 +3254,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>ccb0db69fd82419f</t>
+          <t>0189c2acdf2f4981</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:32.312595Z</t>
+          <t>2026-08-02T08:19:44.224670Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:31.369505Z</t>
+          <t>2026-08-02T08:19:43.195542Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3254,12 +3254,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>0189c2acdf2f4981</t>
+          <t>74d7b0ae490e40d2</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:44.224670Z</t>
+          <t>2026-08-02T10:00:11.648885Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
+          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>ba371790eb45b92bbd2fbfe5a33bbaab7ea5a0f07509006df65e77e32545f142</t>
+          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:43.195542Z</t>
+          <t>2026-08-02T10:00:10.645047Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
-  <autoFilter ref="A1:CO8"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP9" headerRowCount="1">
+  <autoFilter ref="A1:CP9"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -752,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$8)</f>
+        <f>COUNTA('Picks'!$A$2:$A$9)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$8)</f>
+        <f>SUM('Picks'!$BY$2:$BY$9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO8"/>
+  <dimension ref="A1:CP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2704,6 +2714,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2989,6 +3000,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3250,6 +3262,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3511,6 +3524,269 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>23174d6191dd4e48</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:54.976833Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.688017</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.108185</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:07:54.975627Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3083,18 +3083,38 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="Z7" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC7" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:37.832218Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
@@ -3107,7 +3127,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3237,8 +3257,12 @@
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="28" t="n"/>
+      <c r="BQ7" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR7" s="28" t="n">
+        <v>0.44</v>
+      </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
       <c r="BU7" s="25" t="n"/>
@@ -3529,12 +3553,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>23174d6191dd4e48</t>
+          <t>d174431a4b8248b1</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:54.976833Z</t>
+          <t>2026-08-02T15:51:47.398301Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3579,23 +3603,23 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.787402</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.688017</v>
+        <v>0.68794</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.108185</v>
+        <v>0.128469</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
@@ -3621,7 +3645,7 @@
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3705,7 +3729,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3720,7 +3744,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>8b942fbb736985bcb2d3060c95145f67db9c15bdfbfc2955dc5cb5d8a411ff0a</t>
+          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3740,7 +3764,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:54.975627Z</t>
+          <t>2026-08-02T15:51:46.912541Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3750,13 +3774,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.787402</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3786,7 +3810,11 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="n"/>
+      <c r="CP9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP9" headerRowCount="1">
-  <autoFilter ref="A1:CP9"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
+  <autoFilter ref="A1:CQ9"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP9"/>
+  <dimension ref="A1:CQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2715,6 +2725,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3001,6 +3012,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3287,6 +3299,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3549,16 +3562,17 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>d174431a4b8248b1</t>
+          <t>33a58505413e4951</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:47.398301Z</t>
+          <t>2026-08-02T16:15:20.632773Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3612,11 +3626,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.68794</v>
+        <v>0.687866</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.128469</v>
+        <v>0.128395</v>
       </c>
       <c r="R9" s="26" t="n">
         <v>84</v>
@@ -3729,7 +3743,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
+          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3744,7 +3758,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
+          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3764,7 +3778,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:46.912541Z</t>
+          <t>2026-08-02T16:15:20.152893Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3810,7 +3824,8 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="inlineStr">
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3567,12 +3567,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>33a58505413e4951</t>
+          <t>5b00481b44fe4d91</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:20.632773Z</t>
+          <t>2026-08-02T16:53:39.730207Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
+          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>dd15133f8ac3980e0e8f9507ceb080d57ad35a633e2d504e0df7fc9cdc098a3f</t>
+          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:20.152893Z</t>
+          <t>2026-08-02T16:53:39.258654Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
-  <autoFilter ref="A1:CQ9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ8" headerRowCount="1">
+  <autoFilter ref="A1:CQ8"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$9)</f>
+        <f>COUNTA('Picks'!$A$2:$A$8)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$9)</f>
+        <f>SUM('Picks'!$BY$2:$BY$8)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ9"/>
+  <dimension ref="A1:CQ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3564,273 +3564,6 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>5b00481b44fe4d91</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:39.730207Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>69530</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.687866</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.128395</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>3b481b72458f95998f81ca892704b4ac7dca0dff8b1583067f4c8fae4d84ff0d</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:39.258654Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN9" s="28" t="n"/>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
-      <c r="CB9" s="24" t="n"/>
-      <c r="CC9" s="24" t="n"/>
-      <c r="CD9" s="24" t="n"/>
-      <c r="CE9" s="24" t="n"/>
-      <c r="CF9" s="24" t="n"/>
-      <c r="CG9" s="24" t="n"/>
-      <c r="CH9" s="24" t="n"/>
-      <c r="CI9" s="24" t="n"/>
-      <c r="CJ9" s="24" t="n"/>
-      <c r="CK9" s="24" t="n"/>
-      <c r="CL9" s="24" t="n"/>
-      <c r="CM9" s="24" t="n"/>
-      <c r="CN9" s="24" t="n"/>
-      <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ8" headerRowCount="1">
-  <autoFilter ref="A1:CQ8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
+  <autoFilter ref="A1:CQ9"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$8)</f>
+        <f>COUNTA('Picks'!$A$2:$A$9)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$8)</f>
+        <f>SUM('Picks'!$BY$2:$BY$9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ8"/>
+  <dimension ref="A1:CQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3564,6 +3564,273 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>558bacc8b8ca444b</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:47.353360Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.687866</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.128395</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:46.828865Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -3567,12 +3567,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>558bacc8b8ca444b</t>
+          <t>f821321a341c4c82</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:47.353360Z</t>
+          <t>2026-08-02T18:09:15.539608Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>bcd7d4bdd1e2218dd22c32e053e9e1e56eeed1afdf8b775edd90e5369a90ae7e</t>
+          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:46.828865Z</t>
+          <t>2026-08-02T18:09:15.062801Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
-  <autoFilter ref="A1:CQ9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ8" headerRowCount="1">
+  <autoFilter ref="A1:CQ8"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$9)</f>
+        <f>COUNTA('Picks'!$A$2:$A$8)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$9)</f>
+        <f>SUM('Picks'!$BY$2:$BY$8)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ9"/>
+  <dimension ref="A1:CQ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3564,273 +3564,6 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>f821321a341c4c82</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:15.539608Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>69530</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.687866</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.128395</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>84</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>GLYPH</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>PlayTime</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:15.062801Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>-127</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>1.787402</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.5594710000000001</v>
-      </c>
-      <c r="BN9" s="28" t="n"/>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
-      <c r="CB9" s="24" t="n"/>
-      <c r="CC9" s="24" t="n"/>
-      <c r="CD9" s="24" t="n"/>
-      <c r="CE9" s="24" t="n"/>
-      <c r="CF9" s="24" t="n"/>
-      <c r="CG9" s="24" t="n"/>
-      <c r="CH9" s="24" t="n"/>
-      <c r="CI9" s="24" t="n"/>
-      <c r="CJ9" s="24" t="n"/>
-      <c r="CK9" s="24" t="n"/>
-      <c r="CL9" s="24" t="n"/>
-      <c r="CM9" s="24" t="n"/>
-      <c r="CN9" s="24" t="n"/>
-      <c r="CO9" s="24" t="n"/>
-      <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ8" headerRowCount="1">
-  <autoFilter ref="A1:CQ8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
+  <autoFilter ref="A1:CQ9"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$8)</f>
+        <f>COUNTA('Picks'!$A$2:$A$9)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$8)</f>
+        <f>SUM('Picks'!$BY$2:$BY$9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ8"/>
+  <dimension ref="A1:CQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3564,6 +3564,273 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>f0635319ce044dcb</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:04.078583Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.687866</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.128395</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>GLYPH</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:03.516712Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ9" headerRowCount="1">
-  <autoFilter ref="A1:CQ9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
+  <autoFilter ref="A1:CQ15"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$9)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$9)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ9"/>
+  <dimension ref="A1:CQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3382,18 +3382,38 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="Z8" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC8" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:26:56.858449Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
@@ -3406,7 +3426,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3536,8 +3556,12 @@
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
+      <c r="BQ8" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR8" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
       <c r="BU8" s="25" t="n"/>
@@ -3567,12 +3591,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>f0635319ce044dcb</t>
+          <t>56abab72389b4452</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:04.078583Z</t>
+          <t>2026-08-03T04:20:25.162543Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3617,23 +3641,23 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-127</v>
+        <v>-170</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.588235</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.62963</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.687866</v>
+        <v>0.688438</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.128395</v>
+        <v>0.058808</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
@@ -3645,21 +3669,41 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="Z9" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC9" s="30" t="n">
+        <v>1.1765</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:06:56.862820Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3743,7 +3787,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3758,7 +3802,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3778,7 +3822,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:03.516712Z</t>
+          <t>2026-08-03T04:20:21.088131Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3788,19 +3832,23 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-127</v>
+        <v>-170</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.588235</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.62963</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
       <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
+      <c r="BQ9" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR9" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
       <c r="BU9" s="25" t="n"/>
@@ -3831,6 +3879,1680 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>38208d33e6cc491d</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:33.049242Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.622594</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.231969</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB10" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC10" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:56:06.930565Z</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-lgd-1win-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:30.412423Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR10" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>570983c1503a4b3b</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:35.070004Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.75532</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.05562</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="AC11" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:55:47.665015Z</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-re-lgd-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.121525Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>adc2bab7d75c44b7</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:35.070004Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.571416</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:16.043408Z</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-flc-bb-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Team Falcons</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.684542Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>a6bc2b15012f4298</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>70891</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.720685</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.020985</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-og-bb-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:39.542403Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>2c4021865cc3435a</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>70684</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.701803</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.092428</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:40.034960Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>d95695f45e8441b8</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.678151Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>71323</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.63019</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.050358</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T02:00:41.112906Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
-  <autoFilter ref="A1:CQ15"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR14" headerRowCount="1">
+  <autoFilter ref="A1:CR14"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ15"/>
+  <dimension ref="A1:CR14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2726,6 +2736,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3013,6 +3024,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3300,6 +3312,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3587,6 +3600,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3873,7 +3887,8 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4164,7 +4179,8 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4455,7 +4471,8 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4746,7 +4763,8 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4755,22 +4773,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>a6bc2b15012f4298</t>
+          <t>b607d71b19bc4d92</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
+          <t>2026-08-04T08:56:24.176296Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T09:00:00Z</t>
+          <t>2026-08-04T11:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>70891</t>
+          <t>70684</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4780,12 +4798,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4795,7 +4813,7 @@
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J13" s="25" t="n"/>
@@ -4805,23 +4823,23 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-233</v>
+        <v>-138</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.724638</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.579832</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.720685</v>
+        <v>0.701803</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.020985</v>
+        <v>0.121971</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="S13" s="29" t="n">
         <v>2</v>
@@ -4847,7 +4865,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-og-bb-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4888,32 +4906,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4931,7 +4949,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4946,7 +4964,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4966,7 +4984,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:39.542403Z</t>
+          <t>2026-08-04T08:56:22.344795Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4976,13 +4994,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-233</v>
+        <v>-138</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.724638</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.579832</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -5013,7 +5031,8 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5022,22 +5041,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>2c4021865cc3435a</t>
+          <t>fb8a0f1fa69e44b5</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
+          <t>2026-08-04T08:56:24.176296Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T11:00:00Z</t>
+          <t>2026-08-04T14:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>70684</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5047,12 +5066,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5062,7 +5081,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -5072,26 +5091,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.701803</v>
+        <v>0.63019</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.092428</v>
+        <v>0.03019</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5114,7 +5133,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5155,32 +5174,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5198,7 +5217,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5213,7 +5232,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
+          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5233,7 +5252,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:40.034960Z</t>
+          <t>2026-08-04T08:56:23.442743Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5243,13 +5262,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5280,274 +5299,8 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>d95695f45e8441b8</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T02:00:41.678151Z</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>71323</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M15" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N15" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O15" s="28" t="n">
-        <v>0.63019</v>
-      </c>
-      <c r="P15" s="28" t="n"/>
-      <c r="Q15" s="28" t="n">
-        <v>0.050358</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="S15" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
-        </is>
-      </c>
-      <c r="AF15" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG15" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH15" s="24" t="n"/>
-      <c r="AI15" s="31" t="n"/>
-      <c r="AJ15" s="31" t="n"/>
-      <c r="AK15" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN15" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO15" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP15" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AQ15" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AR15" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AS15" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AT15" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AU15" s="24" t="inlineStr">
-        <is>
-          <t>Yakult Brothers</t>
-        </is>
-      </c>
-      <c r="AV15" s="24" t="n"/>
-      <c r="AW15" s="24" t="n"/>
-      <c r="AX15" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY15" s="24" t="n"/>
-      <c r="AZ15" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA15" s="24" t="inlineStr">
-        <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
-        </is>
-      </c>
-      <c r="BB15" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC15" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>126bc67322fe0c2fe0e6fb66aaaaf0e899649029911bf7df0c92c99b0305bbea</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T02:00:41.112906Z</t>
-        </is>
-      </c>
-      <c r="BI15" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ15" s="25" t="n"/>
-      <c r="BK15" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL15" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM15" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN15" s="28" t="n"/>
-      <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
-      <c r="BS15" s="28" t="n"/>
-      <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
-      <c r="BV15" s="29" t="n"/>
-      <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n"/>
-      <c r="BY15" s="27" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
-      <c r="CB15" s="24" t="n"/>
-      <c r="CC15" s="24" t="n"/>
-      <c r="CD15" s="24" t="n"/>
-      <c r="CE15" s="24" t="n"/>
-      <c r="CF15" s="24" t="n"/>
-      <c r="CG15" s="24" t="n"/>
-      <c r="CH15" s="24" t="n"/>
-      <c r="CI15" s="24" t="n"/>
-      <c r="CJ15" s="24" t="n"/>
-      <c r="CK15" s="24" t="n"/>
-      <c r="CL15" s="24" t="n"/>
-      <c r="CM15" s="24" t="n"/>
-      <c r="CN15" s="24" t="n"/>
-      <c r="CO15" s="24" t="n"/>
-      <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR14" headerRowCount="1">
-  <autoFilter ref="A1:CR14"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS14" headerRowCount="1">
+  <autoFilter ref="A1:CS14"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR14"/>
+  <dimension ref="A1:CS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2737,6 +2747,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3025,6 +3036,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3313,6 +3325,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3601,6 +3614,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3888,7 +3902,8 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
-      <c r="CR9" s="24" t="inlineStr">
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4180,7 +4195,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4472,7 +4488,8 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
-      <c r="CR11" s="24" t="inlineStr">
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4764,7 +4781,8 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
-      <c r="CR12" s="24" t="inlineStr">
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4851,18 +4869,38 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="Z13" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC13" s="30" t="n">
+        <v>1.4493</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:01.804516Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
@@ -5005,8 +5043,12 @@
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
+      <c r="BQ13" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR13" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
       <c r="BU13" s="25" t="n"/>
@@ -5032,7 +5074,8 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
-      <c r="CR13" s="24" t="inlineStr">
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5041,12 +5084,12 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>fb8a0f1fa69e44b5</t>
+          <t>0a6ddeb773844727</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.176296Z</t>
+          <t>2026-08-04T12:01:37.365629Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -5217,7 +5260,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5232,7 +5275,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5252,7 +5295,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:23.442743Z</t>
+          <t>2026-08-04T12:01:36.421980Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5300,7 +5343,8 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS14" headerRowCount="1">
-  <autoFilter ref="A1:CS14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS19" headerRowCount="1">
+  <autoFilter ref="A1:CS19"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$19)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$19,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$19,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")/(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$19)/SUM('Picks'!$BX$2:$BX$19),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$19)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$19,"&lt;&gt;",'Picks'!$AB$2:$AB$19),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$19,'Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS14"/>
+  <dimension ref="A1:CS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5162,18 +5162,38 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:50.618209Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
@@ -5186,7 +5206,7 @@
       </c>
       <c r="AG14" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH14" s="24" t="n"/>
@@ -5316,8 +5336,12 @@
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5350,6 +5374,1351 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>77b840baaab6494f</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.500216</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.049766</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:08.611098Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>b5b4e021955b45bc</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.658681</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.128165</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.196950Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>603347ca47634cff</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.806217</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.115815</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.769926Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>25db571091f54b2a</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.528647</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.078197</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.316562Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>da12cff095434235</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.611725</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.211725</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.870839Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -5455,18 +5455,38 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:18.710149Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
@@ -5609,8 +5629,12 @@
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
-      <c r="BR15" s="28" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5724,18 +5748,38 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:51:54.211383Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
@@ -5748,7 +5792,7 @@
       </c>
       <c r="AG16" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH16" s="24" t="n"/>
@@ -5878,8 +5922,12 @@
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -5915,12 +5963,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>603347ca47634cff</t>
+          <t>284b6a66a0c44106</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T10:46:31.198892Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -5965,23 +6013,23 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-223</v>
+        <v>-203</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.492611</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.669967</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.806217</v>
+        <v>0.805779</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.115815</v>
+        <v>0.135812</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>2</v>
@@ -6007,7 +6055,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6091,7 +6139,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -6106,7 +6154,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6126,7 +6174,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:09.769926Z</t>
+          <t>2026-08-05T10:46:27.725458Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6136,13 +6184,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-223</v>
+        <v>-203</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.492611</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.669967</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -6184,12 +6232,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>25db571091f54b2a</t>
+          <t>c9ffcd1582e74505</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T13:56:09.744515Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6234,23 +6282,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.429185</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.528647</v>
+        <v>0.528031</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.078197</v>
+        <v>0.098846</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>1</v>
@@ -6276,7 +6324,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6360,7 +6408,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6375,7 +6423,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6395,7 +6443,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:10.316562Z</t>
+          <t>2026-08-05T13:56:07.743708Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6405,13 +6453,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.429185</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6453,12 +6501,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>da12cff095434235</t>
+          <t>a4e71f07bc984297</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-05T13:56:09.744515Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6512,11 +6560,11 @@
         <v>0.4</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.611725</v>
+        <v>0.611634</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.211725</v>
+        <v>0.211634</v>
       </c>
       <c r="R19" s="26" t="n">
         <v>100</v>
@@ -6629,7 +6677,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6644,7 +6692,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6664,7 +6712,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:10.870839Z</t>
+          <t>2026-08-05T13:56:08.266131Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS19" headerRowCount="1">
-  <autoFilter ref="A1:CS19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS23" headerRowCount="1">
+  <autoFilter ref="A1:CS23"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$19)</f>
+        <f>COUNTA('Picks'!$A$2:$A$23)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$19,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")/(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$19)/SUM('Picks'!$BX$2:$BX$19),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$19)</f>
+        <f>SUM('Picks'!$BY$2:$BY$23)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$19,"&lt;&gt;",'Picks'!$AB$2:$AB$19),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$19,'Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6041,18 +6041,38 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:19.563746Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
@@ -6195,8 +6215,12 @@
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.67</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6232,12 +6256,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>c9ffcd1582e74505</t>
+          <t>f662f1f9c7f9470a</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:09.744515Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6282,23 +6306,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.440529</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.528031</v>
+        <v>0.527212</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.098846</v>
+        <v>0.086683</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>1</v>
@@ -6310,21 +6334,35 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:04.657614Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6334,7 +6372,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6408,7 +6446,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6423,7 +6461,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6443,7 +6481,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:07.743708Z</t>
+          <t>2026-08-06T00:24:35.411288Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6453,13 +6491,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.440529</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6501,12 +6539,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>a4e71f07bc984297</t>
+          <t>b7605df98a074b62</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:09.744515Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6551,20 +6589,20 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.4</v>
+        <v>0.429185</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.611634</v>
+        <v>0.61125</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.211634</v>
+        <v>0.182065</v>
       </c>
       <c r="R19" s="26" t="n">
         <v>100</v>
@@ -6579,21 +6617,35 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:06.215732Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6677,7 +6729,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6692,7 +6744,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>b3a79bf604f63d4a2983de19714e62f9f67a55d4fa57ab078402dbd8e247c624</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6712,7 +6764,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:08.266131Z</t>
+          <t>2026-08-06T00:24:35.868255Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6722,13 +6774,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.4</v>
+        <v>0.429185</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6767,6 +6819,1130 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>ddc8da4bf3474fbd</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:31.608591Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>71682</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.655357</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.08454200000000001</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:21.123639Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-z10-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:28.583196Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>bcfaf2734c4a4ea1</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.357961Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.534269</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.134269</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:05.107086Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-ill-stx-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.860338Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>1564e18df25242d4</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>72729</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.645469</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.265241</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-pr-stx-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.650443Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>b8f0833605324a42</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.158135Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.681484</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.301256</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:55.156966Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -7408,12 +7408,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>1564e18df25242d4</t>
+          <t>68ec8d4b4a5b46a2</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:55.158135Z</t>
+          <t>2026-08-07T18:31:07.919250Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7458,20 +7458,20 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.469484</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.645469</v>
+        <v>0.665399</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.265241</v>
+        <v>0.195915</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>100</v>
@@ -7500,7 +7500,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-pr-stx-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-dota2-pr-stx-2026-08-08).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:54.650443Z</t>
+          <t>2026-08-07T18:31:07.387751Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7629,13 +7629,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.469484</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7677,12 +7677,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>b8f0833605324a42</t>
+          <t>ed188dc582d04ab5</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:55.158135Z</t>
+          <t>2026-08-07T18:31:07.919250Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7727,26 +7727,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.409836</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.681484</v>
+        <v>0.681177</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.301256</v>
+        <v>0.271341</v>
       </c>
       <c r="R23" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>c3ccf6a5a853bf09f9c7ad7a3e7bb20f0df6d66be999c1fcc3b13debd13b244b</t>
+          <t>7611cb925b0bdd8cda78eee9a465c4db63ed56bf3e0e41982af2c70978a81fdb</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:55.156966Z</t>
+          <t>2026-08-07T18:31:07.918561Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7898,13 +7898,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.409836</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS14" headerRowCount="1">
-  <autoFilter ref="A1:CS14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS26" headerRowCount="1">
+  <autoFilter ref="A1:CS26"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$26)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$26)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS14"/>
+  <dimension ref="A1:CS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5162,18 +5162,38 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:50.618209Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
@@ -5186,7 +5206,7 @@
       </c>
       <c r="AG14" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH14" s="24" t="n"/>
@@ -5316,8 +5336,12 @@
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="28" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5350,6 +5374,3502 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>77b840baaab6494f</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>72079</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.500216</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.049766</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:18:18.710149Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Team Resilience</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:08.611098Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>b5b4e021955b45bc</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:12.341207Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>71970</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.658681</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.128165</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:51:54.211383Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>BetBoom Team</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>1win</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:09.196950Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>284b6a66a0c44106</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:31.198892Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.805779</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.135812</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:19.563746Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Yakult Brothers</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>PlayTime</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:46:27.725458Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>f662f1f9c7f9470a</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.791267Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.527212</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.086683</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:04.657614Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.411288Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>b7605df98a074b62</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:36.791267Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>70648</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.61125</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.182065</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:06.215732Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>RE.Arise</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:35.868255Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>ddc8da4bf3474fbd</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:31.608591Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>71682</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.655357</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.08454200000000001</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>1.3158</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:21.123639Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-z10-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Zero Tenacity</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:05:28.583196Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>bcfaf2734c4a4ea1</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:24.357961Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>71775</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.534269</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.134269</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:05.107086Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-ill-stx-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Team Syntax</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:20.860338Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>45a61894cd4649f1</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:53.607771Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>74329</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.694921</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.274753</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:14.743910Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>No Hoodwink</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Ilbirs eSports</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:52.173653Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>01ca169d9c424db6</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:53.607771Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>74944</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.533843</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.143218</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>0.009375</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:16.134540Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-fts-pckcp-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>PuckChamp</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>FTS</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:07:52.761230Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>9b6f24dfab3648db</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:14.399564Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>76395</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.617196</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.166746</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:33:35.786710Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-pr-mouz-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Power Rangers</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:11.396742Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>60856079a65f46ee</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:14.399564Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>76396</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.5843469999999999</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.08434700000000001</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:09:06.403801Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-yes-lvlup-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T05:41:13.718619Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>be73ecddea644b15</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:28.832657Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>79381</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.5450159999999999</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.094566</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:33:48.625425Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-re-2026-08-12).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Level UP</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:23.388322Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS26" headerRowCount="1">
-  <autoFilter ref="A1:CS26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS27" headerRowCount="1">
+  <autoFilter ref="A1:CS27"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$26)</f>
+        <f>COUNTA('Picks'!$A$2:$A$27)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$26)</f>
+        <f>SUM('Picks'!$BY$2:$BY$27)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS26"/>
+  <dimension ref="A1:CS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8870,6 +8870,275 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>faa4178a0b9f43fa</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:36.268320Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>77167</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.738453</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.038753</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-ts-xtreme-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Xtreme Gaming</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Team Spirit</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:35.104443Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/dota2.xlsx
+++ b/data/gated_research/dota2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS27" headerRowCount="1">
-  <autoFilter ref="A1:CS27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS18" headerRowCount="1">
+  <autoFilter ref="A1:CS18"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$27)</f>
+        <f>COUNTA('Picks'!$A$2:$A$18)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$27,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$18,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")/(COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"win")+COUNTIFS('Picks'!$BX$2:$BX$27,"&gt;0",'Picks'!$V$2:$V$27,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")/(COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"win")+COUNTIFS('Picks'!$BX$2:$BX$18,"&gt;0",'Picks'!$V$2:$V$18,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$27)/SUM('Picks'!$BX$2:$BX$27),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$18)/SUM('Picks'!$BX$2:$BX$18),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$27)</f>
+        <f>SUM('Picks'!$BY$2:$BY$18)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$27,"&lt;&gt;",'Picks'!$AB$2:$AB$27),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$18,"&lt;&gt;",'Picks'!$AB$2:$AB$18),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$27,'Picks'!$AM$2:$AM$27,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$18,'Picks'!$AM$2:$AM$18,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A14,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A14,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A15,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A15,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled",'Picks'!$V$2:$V$27,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled",'Picks'!$V$2:$V$18,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$27,'Picks'!$H$2:$H$27,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$18,'Picks'!$H$2:$H$18,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$27,'Picks'!$H$2:$H$27,$A16,'Picks'!$U$2:$U$27,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$18,'Picks'!$H$2:$H$18,$A16,'Picks'!$U$2:$U$18,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS27"/>
+  <dimension ref="A1:CS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1606,22 +1606,22 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>e5513af8c76d4b03</t>
+          <t>77b840baaab6494f</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T10:46:51.141594Z</t>
+          <t>2026-08-05T04:38:12.341207Z</t>
         </is>
       </c>
       <c r="C2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T11:00:00Z</t>
+          <t>2026-08-05T08:00:00Z</t>
         </is>
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
-          <t>64818</t>
+          <t>72079</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>Enjoy</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="I2" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J2" s="25" t="n"/>
@@ -1656,30 +1656,30 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="O2" s="28" t="n">
-        <v>0.675115</v>
+        <v>0.500216</v>
       </c>
       <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
-        <v>0.214286</v>
+        <v>0.049766</v>
       </c>
       <c r="R2" s="26" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="S2" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U2" s="24" t="inlineStr">
@@ -1693,32 +1693,32 @@
         </is>
       </c>
       <c r="W2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X2" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AA2" s="28" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AB2" s="28" t="n">
-        <v>-0.000829</v>
+        <v>-0.00045</v>
       </c>
       <c r="AC2" s="30" t="n">
-        <v>2.34</v>
+        <v>1.22</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T16:45:02.553574Z</t>
+          <t>2026-08-05T10:18:18.710149Z</t>
         </is>
       </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-dota2-enjoy-glyph-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
         </is>
       </c>
       <c r="AF2" s="31" t="inlineStr">
@@ -1759,32 +1759,32 @@
       </c>
       <c r="AP2" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AQ2" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AR2" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AS2" s="24" t="inlineStr">
         <is>
-          <t>Enjoy</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AT2" s="24" t="inlineStr">
         <is>
-          <t>Enjoy</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AU2" s="24" t="inlineStr">
         <is>
-          <t>Enjoy</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AV2" s="24" t="n"/>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="BA2" s="24" t="inlineStr">
         <is>
-          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
         </is>
       </c>
       <c r="BB2" s="24" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="BC2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD2" s="24" t="inlineStr">
         <is>
-          <t>def433bd75610fad2e6504afeb97fc726ca47b86cda4e8e2a0e49fa44868309d</t>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
         </is>
       </c>
       <c r="BE2" s="24" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="BG2" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T10:46:49.443966Z</t>
+          <t>2026-08-05T04:38:08.611098Z</t>
         </is>
       </c>
       <c r="BI2" s="24" t="inlineStr">
@@ -1847,22 +1847,22 @@
       </c>
       <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BL2" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
       <c r="BP2" s="25" t="n"/>
       <c r="BQ2" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="BR2" s="28" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
@@ -1890,27 +1890,31 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
-      <c r="CS2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>720d6ff896f64777</t>
+          <t>b5b4e021955b45bc</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:44:01.315844Z</t>
+          <t>2026-08-05T04:38:12.341207Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T14:00:00Z</t>
+          <t>2026-08-05T09:00:00Z</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>64929</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -1920,12 +1924,12 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>BetBoom Team</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -1945,30 +1949,30 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>156</v>
+        <v>-113</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>2.56</v>
+        <v>1.884956</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.530516</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.610359</v>
+        <v>0.658681</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>0.219734</v>
+        <v>0.128165</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="S3" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1978,36 +1982,36 @@
       </c>
       <c r="V3" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X3" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n">
-        <v>156</v>
+        <v>-113</v>
       </c>
       <c r="AA3" s="28" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="AB3" s="28" t="n">
-        <v>-0.000625</v>
+        <v>-0.000516</v>
       </c>
       <c r="AC3" s="30" t="n">
-        <v>2.34</v>
+        <v>-1.75</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T19:51:28.507069Z</t>
+          <t>2026-08-05T13:51:54.211383Z</t>
         </is>
       </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-yb-z10-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -2017,7 +2021,7 @@
       </c>
       <c r="AG3" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH3" s="24" t="n"/>
@@ -2048,32 +2052,32 @@
       </c>
       <c r="AP3" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>BetBoom Team</t>
         </is>
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>BetBoom Team</t>
         </is>
       </c>
       <c r="AR3" s="24" t="inlineStr">
         <is>
-          <t>Zero Tenacity</t>
+          <t>BetBoom Team</t>
         </is>
       </c>
       <c r="AS3" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="AT3" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="AU3" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>1win</t>
         </is>
       </c>
       <c r="AV3" s="24" t="n"/>
@@ -2091,7 +2095,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2101,12 +2105,12 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
+          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2121,12 +2125,12 @@
       </c>
       <c r="BG3" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:43:57.933952Z</t>
+          <t>2026-08-05T04:38:09.196950Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2136,22 +2140,22 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>156</v>
+        <v>-113</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>2.56</v>
+        <v>1.884956</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.530516</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
       <c r="BQ3" s="27" t="n">
-        <v>2.56</v>
+        <v>1.884956</v>
       </c>
       <c r="BR3" s="28" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
@@ -2179,27 +2183,31 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
-      <c r="CS3" s="24" t="n"/>
+      <c r="CS3" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>0938e25298a64dae</t>
+          <t>284b6a66a0c44106</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:44:01.315844Z</t>
+          <t>2026-08-05T10:46:31.198892Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T14:00:00Z</t>
+          <t>2026-08-05T12:00:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>64928</t>
+          <t>72080</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2209,12 +2217,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>Xtreme Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J4" s="25" t="n"/>
@@ -2234,30 +2242,30 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>-127</v>
+        <v>-203</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.492611</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.669967</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.701925</v>
+        <v>0.805779</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>0.142454</v>
+        <v>0.135812</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="S4" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2267,7 +2275,7 @@
       </c>
       <c r="V4" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W4" s="26" t="n">
@@ -2278,25 +2286,25 @@
       </c>
       <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n">
-        <v>-127</v>
+        <v>-203</v>
       </c>
       <c r="AA4" s="28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="AB4" s="28" t="n">
-        <v>0.000529</v>
+        <v>3.3e-05</v>
       </c>
       <c r="AC4" s="30" t="n">
-        <v>-2</v>
+        <v>0.9852</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T23:28:46.755247Z</t>
+          <t>2026-08-05T17:01:19.563746Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-dota2-xtreme-lgd-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2306,7 +2314,7 @@
       </c>
       <c r="AG4" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH4" s="24" t="n"/>
@@ -2337,32 +2345,32 @@
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>Xtreme Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>Xtreme Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>Xtreme Gaming</t>
+          <t>PlayTime</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2380,7 +2388,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2390,12 +2398,12 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>b5798e8e2d651ab79c8db316f3ec8a564cab27653a02daab82555f6e9f330ac3</t>
+          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2410,12 +2418,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:43:58.701955Z</t>
+          <t>2026-08-05T10:46:27.725458Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2425,22 +2433,22 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>-127</v>
+        <v>-203</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.492611</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.669967</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
       <c r="BP4" s="25" t="n"/>
       <c r="BQ4" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.492611</v>
       </c>
       <c r="BR4" s="28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
@@ -2468,27 +2476,31 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
-      <c r="CS4" s="24" t="n"/>
+      <c r="CS4" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>631326b56379473e</t>
+          <t>f662f1f9c7f9470a</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T03:02:50.460010Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T05:00:00Z</t>
+          <t>2026-08-06T09:00:00Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>67530</t>
+          <t>70575</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2498,12 +2510,12 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>Midas Club</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2523,30 +2535,30 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>-150</v>
+        <v>127</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.27</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.6</v>
+        <v>0.440529</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.630791</v>
+        <v>0.527212</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.030791</v>
+        <v>0.086683</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="S5" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2556,30 +2568,30 @@
       </c>
       <c r="V5" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X5" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T10:16:06.748137Z</t>
+          <t>2026-08-06T18:57:04.657614Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-midas-tr-2026-08-01).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2589,7 +2601,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2620,32 +2632,32 @@
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>Midas Club</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>Midas Club</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>Midas Club</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2663,7 +2675,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2673,12 +2685,12 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>70c4a9b222a6dac9c1b0737621af569fa1e0e955085795442f7ac4d19191488f</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2693,12 +2705,12 @@
       </c>
       <c r="BG5" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T03:02:45.273136Z</t>
+          <t>2026-08-06T00:24:35.411288Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2708,13 +2720,13 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>-150</v>
+        <v>127</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.27</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.6</v>
+        <v>0.440529</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
@@ -2747,27 +2759,31 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
-      <c r="CS5" s="24" t="n"/>
+      <c r="CS5" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>9518099e84cd4bb6</t>
+          <t>b7605df98a074b62</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T06:42:17.908342Z</t>
+          <t>2026-08-06T00:24:36.791267Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T08:00:00Z</t>
+          <t>2026-08-06T12:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>67531</t>
+          <t>70648</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2777,12 +2793,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2792,7 +2808,7 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J6" s="25" t="n"/>
@@ -2802,30 +2818,30 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-178</v>
+        <v>133</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.33</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.429185</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.685333</v>
+        <v>0.61125</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.045045</v>
+        <v>0.182065</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="S6" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2835,7 +2851,7 @@
       </c>
       <c r="V6" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W6" s="26" t="n">
@@ -2845,26 +2861,20 @@
         <v>1</v>
       </c>
       <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="AA6" s="28" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AB6" s="28" t="n">
-        <v>-0.000288</v>
-      </c>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
       <c r="AC6" s="30" t="n">
-        <v>-2</v>
+        <v>1.995</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T13:41:26.204467Z</t>
+          <t>2026-08-06T18:57:06.215732Z</t>
         </is>
       </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-dota2-re-pla-2026-08-01).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2874,7 +2884,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2905,32 +2915,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>RE.Arise</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2948,7 +2958,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2958,12 +2968,12 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>752abd49fc5066bbf6c0b57bc44412069a390e80fbe7ec7ad0c39f984fb62854</t>
+          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2978,12 +2988,12 @@
       </c>
       <c r="BG6" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T06:42:13.849047Z</t>
+          <t>2026-08-06T00:24:35.868255Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2993,23 +3003,19 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-178</v>
+        <v>133</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.33</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.429185</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BR6" s="28" t="n">
-        <v>0.64</v>
-      </c>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
       <c r="BU6" s="25" t="n"/>
@@ -3036,27 +3042,31 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
-      <c r="CS6" s="24" t="n"/>
+      <c r="CS6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>ed3b2bbfc78f4fd7</t>
+          <t>ddc8da4bf3474fbd</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:32.312595Z</t>
+          <t>2026-08-07T06:05:31.608591Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:00:00Z</t>
+          <t>2026-08-07T09:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>68446</t>
+          <t>71682</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -3066,12 +3076,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>Yellow Submarine</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3081,7 +3091,7 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -3091,30 +3101,30 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>127</v>
+        <v>-133</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.27</v>
+        <v>1.75188</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.570815</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.576085</v>
+        <v>0.655357</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.135556</v>
+        <v>0.08454200000000001</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U7" s="24" t="inlineStr">
@@ -3124,7 +3134,7 @@
       </c>
       <c r="V7" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W7" s="26" t="n">
@@ -3135,25 +3145,25 @@
       </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n">
-        <v>127</v>
+        <v>-133</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="AB7" s="28" t="n">
-        <v>-0.000529</v>
+        <v>-0.000815</v>
       </c>
       <c r="AC7" s="30" t="n">
-        <v>-1.25</v>
+        <v>1.3158</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:53:37.832218Z</t>
+          <t>2026-08-07T12:14:21.123639Z</t>
         </is>
       </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-yes-tr-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-z10-2026-08-07).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3163,7 +3173,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3194,32 +3204,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Zero Tenacity</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>Yellow Submarine</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>Yellow Submarine</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>Yellow Submarine</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3237,7 +3247,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3247,12 +3257,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>9e5f3e455da6fe4a2d8dcc8c9466846303c6541f69893fd12aeb76cf2c918868</t>
+          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3267,12 +3277,12 @@
       </c>
       <c r="BG7" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:30.813424Z</t>
+          <t>2026-08-07T06:05:28.583196Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3282,22 +3292,22 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>127</v>
+        <v>-133</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.27</v>
+        <v>1.75188</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.570815</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
       <c r="BQ7" s="27" t="n">
-        <v>2.27</v>
+        <v>1.75188</v>
       </c>
       <c r="BR7" s="28" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
@@ -3325,27 +3335,31 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
-      <c r="CS7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>74d7b0ae490e40d2</t>
+          <t>bcfaf2734c4a4ea1</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:11.648885Z</t>
+          <t>2026-08-07T09:11:24.357961Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T11:00:00Z</t>
+          <t>2026-08-07T12:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>69232</t>
+          <t>71775</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3355,12 +3369,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3370,7 +3384,7 @@
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J8" s="25" t="n"/>
@@ -3380,30 +3394,30 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.4</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.702765</v>
+        <v>0.534269</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.212569</v>
+        <v>0.134269</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U8" s="24" t="inlineStr">
@@ -3417,32 +3431,32 @@
         </is>
       </c>
       <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X8" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="AA8" s="28" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
       <c r="AB8" s="28" t="n">
-        <v>-0.000196</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="30" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:26:56.858449Z</t>
+          <t>2026-08-07T15:20:05.107086Z</t>
         </is>
       </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-dota2-rnx-yb-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-ill-stx-2026-08-07).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3483,32 +3497,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Syntax</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>REKONIX</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3526,7 +3540,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3536,12 +3550,12 @@
       </c>
       <c r="BC8" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>d60687e602976b4a2779a4ff6a5f8f825a178fa4df1e53dc8ee5e3eeffcc3d8b</t>
+          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3556,12 +3570,12 @@
       </c>
       <c r="BG8" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:10.645047Z</t>
+          <t>2026-08-07T09:11:20.860338Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3571,22 +3585,22 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.4</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
       <c r="BQ8" s="27" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="BR8" s="28" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
@@ -3614,27 +3628,31 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
-      <c r="CS8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>56abab72389b4452</t>
+          <t>45a61894cd4649f1</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T04:20:25.162543Z</t>
+          <t>2026-08-08T04:07:53.607771Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T05:00:00Z</t>
+          <t>2026-08-08T09:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>69530</t>
+          <t>74329</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3644,12 +3662,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3669,30 +3687,30 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-170</v>
+        <v>138</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.38</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.420168</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.688438</v>
+        <v>0.694921</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.058808</v>
+        <v>0.274753</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U9" s="24" t="inlineStr">
@@ -3702,36 +3720,36 @@
       </c>
       <c r="V9" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X9" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n">
-        <v>-170</v>
+        <v>138</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="AB9" s="28" t="n">
-        <v>0.00037</v>
+        <v>-0.000168</v>
       </c>
       <c r="AC9" s="30" t="n">
-        <v>1.1765</v>
+        <v>-2</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:06:56.862820Z</t>
+          <t>2026-08-08T18:35:14.743910Z</t>
         </is>
       </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-pla-glyph-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3741,7 +3759,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3772,32 +3790,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>GLYPH</t>
+          <t>No Hoodwink</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Ilbirs eSports</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3815,7 +3833,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3825,12 +3843,12 @@
       </c>
       <c r="BC9" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3845,12 +3863,12 @@
       </c>
       <c r="BG9" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T04:20:21.088131Z</t>
+          <t>2026-08-08T04:07:52.173653Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3860,22 +3878,22 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-170</v>
+        <v>138</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.38</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.420168</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
       <c r="BP9" s="25" t="n"/>
       <c r="BQ9" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.38</v>
       </c>
       <c r="BR9" s="28" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
@@ -3912,22 +3930,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>38208d33e6cc491d</t>
+          <t>01ca169d9c424db6</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T06:32:33.049242Z</t>
+          <t>2026-08-08T04:07:53.607771Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T09:00:00Z</t>
+          <t>2026-08-08T12:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>70303</t>
+          <t>74944</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3937,12 +3955,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>FTS</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3971,21 +3989,21 @@
         <v>0.390625</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.622594</v>
+        <v>0.533843</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.231969</v>
+        <v>0.143218</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U10" s="24" t="inlineStr">
@@ -3995,36 +4013,36 @@
       </c>
       <c r="V10" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X10" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="AA10" s="28" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="AB10" s="28" t="n">
-        <v>-0.000625</v>
+        <v>0.009375</v>
       </c>
       <c r="AC10" s="30" t="n">
-        <v>-1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:56:06.930565Z</t>
+          <t>2026-08-08T18:35:16.134540Z</t>
         </is>
       </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-lgd-1win-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-fts-pckcp-2026-08-08).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -4034,7 +4052,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -4065,32 +4083,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>PuckChamp</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>FTS</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>FTS</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>FTS</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -4108,7 +4126,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4118,12 +4136,12 @@
       </c>
       <c r="BC10" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4138,12 +4156,12 @@
       </c>
       <c r="BG10" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T06:32:30.412423Z</t>
+          <t>2026-08-08T04:07:52.761230Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4165,10 +4183,10 @@
       <c r="BO10" s="28" t="n"/>
       <c r="BP10" s="25" t="n"/>
       <c r="BQ10" s="27" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BR10" s="28" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
@@ -4205,22 +4223,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>570983c1503a4b3b</t>
+          <t>9b6f24dfab3648db</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:30:35.070004Z</t>
+          <t>2026-08-10T05:41:14.399564Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-10T09:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>70380</t>
+          <t>76395</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4230,12 +4248,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Power Rangers</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4245,7 +4263,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4255,30 +4273,30 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-233</v>
+        <v>122</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.22</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.45045</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.75532</v>
+        <v>0.617196</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.05562</v>
+        <v>0.166746</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U11" s="24" t="inlineStr">
@@ -4292,32 +4310,32 @@
         </is>
       </c>
       <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n">
-        <v>-233</v>
+        <v>122</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="AB11" s="28" t="n">
-        <v>0.0003</v>
+        <v>-0.00045</v>
       </c>
       <c r="AC11" s="30" t="n">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T22:55:47.665015Z</t>
+          <t>2026-08-10T16:33:35.786710Z</t>
         </is>
       </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-re-lgd-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-pr-mouz-2026-08-10).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4358,32 +4376,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>LGD Gaming</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Power Rangers</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Power Rangers</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Power Rangers</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4401,7 +4419,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4411,12 +4429,12 @@
       </c>
       <c r="BC11" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4431,12 +4449,12 @@
       </c>
       <c r="BG11" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:30:33.121525Z</t>
+          <t>2026-08-10T05:41:11.396742Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4446,22 +4464,22 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-233</v>
+        <v>122</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.22</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.45045</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
       <c r="BQ11" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.22</v>
       </c>
       <c r="BR11" s="28" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
@@ -4498,22 +4516,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>adc2bab7d75c44b7</t>
+          <t>60856079a65f46ee</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:30:35.070004Z</t>
+          <t>2026-08-10T05:41:14.399564Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-10T15:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>76396</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4523,12 +4541,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4538,7 +4556,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4548,30 +4566,30 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.884956</v>
+        <v>2</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.5</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.571416</v>
+        <v>0.5843469999999999</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.0409</v>
+        <v>0.08434700000000001</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
@@ -4585,32 +4603,32 @@
         </is>
       </c>
       <c r="W12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X12" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="28" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AB12" s="28" t="n">
-        <v>-0.000516</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T19:52:16.043408Z</t>
+          <t>2026-08-11T13:09:06.403801Z</t>
         </is>
       </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-flc-bb-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-yes-lvlup-2026-08-10).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4651,32 +4669,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Team Falcons</t>
+          <t>Yellow Submarine</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4694,7 +4712,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4704,12 +4722,12 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4724,12 +4742,12 @@
       </c>
       <c r="BG12" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:30:33.684542Z</t>
+          <t>2026-08-10T05:41:13.718619Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4739,22 +4757,22 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.884956</v>
+        <v>2</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
       <c r="BQ12" s="27" t="n">
-        <v>1.884956</v>
+        <v>2</v>
       </c>
       <c r="BR12" s="28" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
@@ -4791,22 +4809,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>b607d71b19bc4d92</t>
+          <t>be73ecddea644b15</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.176296Z</t>
+          <t>2026-08-12T08:22:28.832657Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T11:00:00Z</t>
+          <t>2026-08-12T09:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>70684</t>
+          <t>79381</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4816,12 +4834,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4841,30 +4859,30 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-138</v>
+        <v>122</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.22</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.45045</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.701803</v>
+        <v>0.5450159999999999</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.121971</v>
+        <v>0.094566</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U13" s="24" t="inlineStr">
@@ -4885,25 +4903,25 @@
       </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n">
-        <v>-138</v>
+        <v>122</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>0.58</v>
+        <v>0.45</v>
       </c>
       <c r="AB13" s="28" t="n">
-        <v>0.000168</v>
+        <v>-0.00045</v>
       </c>
       <c r="AC13" s="30" t="n">
-        <v>1.4493</v>
+        <v>1.22</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:04:01.804516Z</t>
+          <t>2026-08-12T14:33:48.625425Z</t>
         </is>
       </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-dota2-pla-tr-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-re-2026-08-12).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4944,32 +4962,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Level UP</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4987,7 +5005,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4997,12 +5015,12 @@
       </c>
       <c r="BC13" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>97107a1d2e9f7b705ead2c5fce1c23807f8dd72b6d4856d7fd17103d4393ae99</t>
+          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -5017,12 +5035,12 @@
       </c>
       <c r="BG13" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:22.344795Z</t>
+          <t>2026-08-12T08:22:23.388322Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -5032,22 +5050,22 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-138</v>
+        <v>122</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.22</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.45045</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
       <c r="BQ13" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.22</v>
       </c>
       <c r="BR13" s="28" t="n">
-        <v>0.58</v>
+        <v>0.45</v>
       </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
@@ -5084,22 +5102,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>0a6ddeb773844727</t>
+          <t>52e407a4b55f4fdc</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:01:37.365629Z</t>
+          <t>2026-08-12T21:33:42.422268Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:00:00Z</t>
+          <t>2026-08-13T05:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>71323</t>
+          <t>77167</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5109,12 +5127,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5124,7 +5142,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -5134,30 +5152,30 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-150</v>
+        <v>-233</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.429185</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.6</v>
+        <v>0.6997</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.63019</v>
+        <v>0.738336</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.03019</v>
+        <v>0.038636</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
@@ -5167,7 +5185,7 @@
       </c>
       <c r="V14" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W14" s="26" t="n">
@@ -5177,26 +5195,20 @@
         <v>1</v>
       </c>
       <c r="Y14" s="25" t="n"/>
-      <c r="Z14" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AA14" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB14" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
       <c r="AC14" s="30" t="n">
-        <v>-1.5</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:04:50.618209Z</t>
+          <t>2026-08-13T10:07:17.377045Z</t>
         </is>
       </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-dota2-yb-re-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-ts-xtreme-2026-08-13).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5206,7 +5218,7 @@
       </c>
       <c r="AG14" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH14" s="24" t="n"/>
@@ -5237,32 +5249,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5280,7 +5292,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
+          <t>3a1a2b913a7c526741b38a48f0957f5889bc186a2bd05c8fa45d935778de3be1</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5290,12 +5302,12 @@
       </c>
       <c r="BC14" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>a6c9607e653da0963c1aedbfdf02df93d0e81f5e712085073f323442476b541d</t>
+          <t>3a1a2b913a7c526741b38a48f0957f5889bc186a2bd05c8fa45d935778de3be1</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5310,12 +5322,12 @@
       </c>
       <c r="BG14" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v5</t>
+          <t>dota2-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T12:01:36.421980Z</t>
+          <t>2026-08-12T21:33:41.354194Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5325,23 +5337,19 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-150</v>
+        <v>-233</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.429185</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.6</v>
+        <v>0.6997</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BR14" s="28" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
       <c r="BU14" s="25" t="n"/>
@@ -5377,22 +5385,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>77b840baaab6494f</t>
+          <t>7ef09cb451f946d7</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-13T17:16:24.578466Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T08:00:00Z</t>
+          <t>2026-08-14T02:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>80486</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5402,12 +5410,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Team Yandex</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5427,26 +5435,26 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>122</v>
+        <v>-163</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2.22</v>
+        <v>1.613497</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.619772</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.500216</v>
+        <v>0.6715989999999999</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.049766</v>
+        <v>0.051827</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
@@ -5455,41 +5463,21 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="26" t="n">
-        <v>1</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
       <c r="Y15" s="25" t="n"/>
-      <c r="Z15" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="AA15" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AB15" s="28" t="n">
-        <v>-0.00045</v>
-      </c>
-      <c r="AC15" s="30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD15" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T10:18:18.710149Z</t>
-        </is>
-      </c>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tr-re-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-dota2-ty-liquid-2026-08-14).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5530,32 +5518,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Team Yandex</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Team Yandex</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Team Resilience</t>
+          <t>Team Yandex</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5573,7 +5561,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5588,7 +5576,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5608,7 +5596,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:08.611098Z</t>
+          <t>2026-08-13T17:16:21.311272Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5618,23 +5606,19 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>122</v>
+        <v>-163</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>2.22</v>
+        <v>1.613497</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.619772</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BR15" s="28" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
       <c r="BU15" s="25" t="n"/>
@@ -5670,22 +5654,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>b5b4e021955b45bc</t>
+          <t>ef74cee951b443de</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:12.341207Z</t>
+          <t>2026-08-13T17:16:24.578466Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T09:00:00Z</t>
+          <t>2026-08-14T02:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>71970</t>
+          <t>80487</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5695,12 +5679,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5710,7 +5694,7 @@
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J16" s="25" t="n"/>
@@ -5720,26 +5704,26 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-113</v>
+        <v>-144</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.694444</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.590164</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.658681</v>
+        <v>0.79937</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.128165</v>
+        <v>0.209206</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5748,41 +5732,21 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W16" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="26" t="n">
-        <v>1</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n">
-        <v>-113</v>
-      </c>
-      <c r="AA16" s="28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AB16" s="28" t="n">
-        <v>-0.000516</v>
-      </c>
-      <c r="AC16" s="30" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AD16" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:51:54.211383Z</t>
-        </is>
-      </c>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-1win-bb-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-ts-xtreme-2026-08-14).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5792,7 +5756,7 @@
       </c>
       <c r="AG16" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH16" s="24" t="n"/>
@@ -5823,32 +5787,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>BetBoom Team</t>
+          <t>Xtreme Gaming</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>1win</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5866,7 +5830,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5881,7 +5845,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>2375429151111a3cb0937a48db93b740727ff54a7bd88a5e4f97e0362efce045</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5901,7 +5865,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:09.196950Z</t>
+          <t>2026-08-13T17:16:21.914112Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5911,23 +5875,19 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-113</v>
+        <v>-144</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.694444</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.590164</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n">
-        <v>1.884956</v>
-      </c>
-      <c r="BR16" s="28" t="n">
-        <v>0.53</v>
-      </c>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -5963,22 +5923,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>284b6a66a0c44106</t>
+          <t>f6fc4e3632864851</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:46:31.198892Z</t>
+          <t>2026-08-13T17:16:24.578466Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T12:00:00Z</t>
+          <t>2026-08-14T05:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>72080</t>
+          <t>80587</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5988,12 +5948,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -6003,7 +5963,7 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J17" s="25" t="n"/>
@@ -6013,26 +5973,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-203</v>
+        <v>-113</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.884956</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.530516</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.805779</v>
+        <v>0.630076</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.135812</v>
+        <v>0.09956</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -6041,41 +6001,21 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="26" t="n">
-        <v>1</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n">
-        <v>-203</v>
-      </c>
-      <c r="AA17" s="28" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AB17" s="28" t="n">
-        <v>3.3e-05</v>
-      </c>
-      <c r="AC17" s="30" t="n">
-        <v>0.9852</v>
-      </c>
-      <c r="AD17" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T17:01:19.563746Z</t>
-        </is>
-      </c>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-dota2-pla-yb-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-dota2-tr-og-2026-08-14).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6116,32 +6056,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Yakult Brothers</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>PlayTime</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -6159,7 +6099,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -6174,7 +6114,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>dc641a33858ba89d589d026590c359ae9cf892296ca087b95549769d488c4494</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6194,7 +6134,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:46:27.725458Z</t>
+          <t>2026-08-13T17:16:22.989356Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6204,23 +6144,19 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-203</v>
+        <v>-113</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.884956</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.530516</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n">
-        <v>1.492611</v>
-      </c>
-      <c r="BR17" s="28" t="n">
-        <v>0.67</v>
-      </c>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6256,22 +6192,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>f662f1f9c7f9470a</t>
+          <t>ef4ea1f9a6604ca2</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:24:36.791267Z</t>
+          <t>2026-08-13T17:16:24.578466Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T09:00:00Z</t>
+          <t>2026-08-14T05:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>70575</t>
+          <t>80588</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6281,12 +6217,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Nigma Galaxy</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6296,7 +6232,7 @@
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J18" s="25" t="n"/>
@@ -6306,26 +6242,26 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>127</v>
+        <v>-122</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>2.27</v>
+        <v>1.819672</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.54955</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.527212</v>
+        <v>0.578638</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.086683</v>
+        <v>0.029088</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6334,35 +6270,21 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W18" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="26" t="n">
-        <v>1</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD18" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T18:57:04.657614Z</t>
-        </is>
-      </c>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-dota2-lvlup-rae-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-dota2-lgd-ngx-2026-08-14).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6372,7 +6294,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6403,32 +6325,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Nigma Galaxy</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Nigma Galaxy</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>RE.Arise</t>
+          <t>Nigma Galaxy</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Level UP</t>
+          <t>LGD Gaming</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6446,7 +6368,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6461,7 +6383,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6481,7 +6403,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:24:35.411288Z</t>
+          <t>2026-08-13T17:16:23.502827Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6491,13 +6413,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>127</v>
+        <v>-122</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>2.27</v>
+        <v>1.819672</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.54955</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6536,2609 +6458,6 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>b7605df98a074b62</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T00:24:36.791267Z</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>70648</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L19" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="M19" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="N19" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="O19" s="28" t="n">
-        <v>0.61125</v>
-      </c>
-      <c r="P19" s="28" t="n"/>
-      <c r="Q19" s="28" t="n">
-        <v>0.182065</v>
-      </c>
-      <c r="R19" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S19" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T19" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U19" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
-        <v>1.995</v>
-      </c>
-      <c r="AD19" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T18:57:06.215732Z</t>
-        </is>
-      </c>
-      <c r="AE19" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-dota2-rae-nh-2026-08-06).</t>
-        </is>
-      </c>
-      <c r="AF19" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG19" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH19" s="24" t="n"/>
-      <c r="AI19" s="31" t="n"/>
-      <c r="AJ19" s="31" t="n"/>
-      <c r="AK19" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL19" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM19" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN19" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO19" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP19" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AQ19" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AR19" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AS19" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="AT19" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="AU19" s="24" t="inlineStr">
-        <is>
-          <t>RE.Arise</t>
-        </is>
-      </c>
-      <c r="AV19" s="24" t="n"/>
-      <c r="AW19" s="24" t="n"/>
-      <c r="AX19" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY19" s="24" t="n"/>
-      <c r="AZ19" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA19" s="24" t="inlineStr">
-        <is>
-          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
-        </is>
-      </c>
-      <c r="BB19" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC19" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD19" s="24" t="inlineStr">
-        <is>
-          <t>4b65e86ec6027f3de08417af250975d63d7eb48ed52a953720074a1ff26360df</t>
-        </is>
-      </c>
-      <c r="BE19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG19" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH19" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T00:24:35.868255Z</t>
-        </is>
-      </c>
-      <c r="BI19" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ19" s="25" t="n"/>
-      <c r="BK19" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="BL19" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BM19" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="BN19" s="28" t="n"/>
-      <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
-      <c r="BS19" s="28" t="n"/>
-      <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
-      <c r="BV19" s="29" t="n"/>
-      <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n"/>
-      <c r="BY19" s="27" t="n"/>
-      <c r="BZ19" s="24" t="n"/>
-      <c r="CA19" s="31" t="n"/>
-      <c r="CB19" s="24" t="n"/>
-      <c r="CC19" s="24" t="n"/>
-      <c r="CD19" s="24" t="n"/>
-      <c r="CE19" s="24" t="n"/>
-      <c r="CF19" s="24" t="n"/>
-      <c r="CG19" s="24" t="n"/>
-      <c r="CH19" s="24" t="n"/>
-      <c r="CI19" s="24" t="n"/>
-      <c r="CJ19" s="24" t="n"/>
-      <c r="CK19" s="24" t="n"/>
-      <c r="CL19" s="24" t="n"/>
-      <c r="CM19" s="24" t="n"/>
-      <c r="CN19" s="24" t="n"/>
-      <c r="CO19" s="24" t="n"/>
-      <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="n"/>
-      <c r="CS19" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>ddc8da4bf3474fbd</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T06:05:31.608591Z</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>71682</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L20" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M20" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N20" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O20" s="28" t="n">
-        <v>0.655357</v>
-      </c>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n">
-        <v>0.08454200000000001</v>
-      </c>
-      <c r="R20" s="26" t="n">
-        <v>62</v>
-      </c>
-      <c r="S20" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T20" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U20" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="AA20" s="28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AB20" s="28" t="n">
-        <v>-0.000815</v>
-      </c>
-      <c r="AC20" s="30" t="n">
-        <v>1.3158</v>
-      </c>
-      <c r="AD20" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T12:14:21.123639Z</t>
-        </is>
-      </c>
-      <c r="AE20" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-nh-z10-2026-08-07).</t>
-        </is>
-      </c>
-      <c r="AF20" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG20" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH20" s="24" t="n"/>
-      <c r="AI20" s="31" t="n"/>
-      <c r="AJ20" s="31" t="n"/>
-      <c r="AK20" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL20" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM20" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN20" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO20" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AQ20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AR20" s="24" t="inlineStr">
-        <is>
-          <t>Zero Tenacity</t>
-        </is>
-      </c>
-      <c r="AS20" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AT20" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AU20" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AV20" s="24" t="n"/>
-      <c r="AW20" s="24" t="n"/>
-      <c r="AX20" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY20" s="24" t="n"/>
-      <c r="AZ20" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA20" s="24" t="inlineStr">
-        <is>
-          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
-        </is>
-      </c>
-      <c r="BB20" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC20" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD20" s="24" t="inlineStr">
-        <is>
-          <t>b5735afe41509d1bfa8df2510b921846426862fa58936449e65c5e162a34c4c8</t>
-        </is>
-      </c>
-      <c r="BE20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG20" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH20" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T06:05:28.583196Z</t>
-        </is>
-      </c>
-      <c r="BI20" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ20" s="25" t="n"/>
-      <c r="BK20" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL20" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM20" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN20" s="28" t="n"/>
-      <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BR20" s="28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BS20" s="28" t="n"/>
-      <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
-      <c r="BV20" s="29" t="n"/>
-      <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n"/>
-      <c r="BY20" s="27" t="n"/>
-      <c r="BZ20" s="24" t="n"/>
-      <c r="CA20" s="31" t="n"/>
-      <c r="CB20" s="24" t="n"/>
-      <c r="CC20" s="24" t="n"/>
-      <c r="CD20" s="24" t="n"/>
-      <c r="CE20" s="24" t="n"/>
-      <c r="CF20" s="24" t="n"/>
-      <c r="CG20" s="24" t="n"/>
-      <c r="CH20" s="24" t="n"/>
-      <c r="CI20" s="24" t="n"/>
-      <c r="CJ20" s="24" t="n"/>
-      <c r="CK20" s="24" t="n"/>
-      <c r="CL20" s="24" t="n"/>
-      <c r="CM20" s="24" t="n"/>
-      <c r="CN20" s="24" t="n"/>
-      <c r="CO20" s="24" t="n"/>
-      <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="n"/>
-      <c r="CS20" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>bcfaf2734c4a4ea1</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T09:11:24.357961Z</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>71775</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>Team Syntax</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="M21" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N21" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O21" s="28" t="n">
-        <v>0.534269</v>
-      </c>
-      <c r="P21" s="28" t="n"/>
-      <c r="Q21" s="28" t="n">
-        <v>0.134269</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>87</v>
-      </c>
-      <c r="S21" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U21" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W21" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA21" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB21" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T15:20:05.107086Z</t>
-        </is>
-      </c>
-      <c r="AE21" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-ill-stx-2026-08-07).</t>
-        </is>
-      </c>
-      <c r="AF21" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG21" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH21" s="24" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL21" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN21" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO21" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP21" s="24" t="inlineStr">
-        <is>
-          <t>Team Syntax</t>
-        </is>
-      </c>
-      <c r="AQ21" s="24" t="inlineStr">
-        <is>
-          <t>Team Syntax</t>
-        </is>
-      </c>
-      <c r="AR21" s="24" t="inlineStr">
-        <is>
-          <t>Team Syntax</t>
-        </is>
-      </c>
-      <c r="AS21" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AT21" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AU21" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AV21" s="24" t="n"/>
-      <c r="AW21" s="24" t="n"/>
-      <c r="AX21" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY21" s="24" t="n"/>
-      <c r="AZ21" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA21" s="24" t="inlineStr">
-        <is>
-          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
-        </is>
-      </c>
-      <c r="BB21" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC21" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD21" s="24" t="inlineStr">
-        <is>
-          <t>f9dedaeb469ef593cde46debd4929efce40f56a153d988595b6823ce5dad05ca</t>
-        </is>
-      </c>
-      <c r="BE21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF21" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG21" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH21" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-07T09:11:20.860338Z</t>
-        </is>
-      </c>
-      <c r="BI21" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ21" s="25" t="n"/>
-      <c r="BK21" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="BL21" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM21" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN21" s="28" t="n"/>
-      <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BR21" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BS21" s="28" t="n"/>
-      <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
-      <c r="BV21" s="29" t="n"/>
-      <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
-      <c r="BZ21" s="24" t="n"/>
-      <c r="CA21" s="31" t="n"/>
-      <c r="CB21" s="24" t="n"/>
-      <c r="CC21" s="24" t="n"/>
-      <c r="CD21" s="24" t="n"/>
-      <c r="CE21" s="24" t="n"/>
-      <c r="CF21" s="24" t="n"/>
-      <c r="CG21" s="24" t="n"/>
-      <c r="CH21" s="24" t="n"/>
-      <c r="CI21" s="24" t="n"/>
-      <c r="CJ21" s="24" t="n"/>
-      <c r="CK21" s="24" t="n"/>
-      <c r="CL21" s="24" t="n"/>
-      <c r="CM21" s="24" t="n"/>
-      <c r="CN21" s="24" t="n"/>
-      <c r="CO21" s="24" t="n"/>
-      <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="n"/>
-      <c r="CS21" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>45a61894cd4649f1</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T04:07:53.607771Z</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>74329</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="M22" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="N22" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="O22" s="28" t="n">
-        <v>0.694921</v>
-      </c>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n">
-        <v>0.274753</v>
-      </c>
-      <c r="R22" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S22" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W22" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="AA22" s="28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AB22" s="28" t="n">
-        <v>-0.000168</v>
-      </c>
-      <c r="AC22" s="30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T18:35:14.743910Z</t>
-        </is>
-      </c>
-      <c r="AE22" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-dota2-ill-nh-2026-08-08).</t>
-        </is>
-      </c>
-      <c r="AF22" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG22" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH22" s="24" t="n"/>
-      <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
-      <c r="AK22" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL22" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN22" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO22" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP22" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AQ22" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AR22" s="24" t="inlineStr">
-        <is>
-          <t>No Hoodwink</t>
-        </is>
-      </c>
-      <c r="AS22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AT22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AU22" s="24" t="inlineStr">
-        <is>
-          <t>Ilbirs eSports</t>
-        </is>
-      </c>
-      <c r="AV22" s="24" t="n"/>
-      <c r="AW22" s="24" t="n"/>
-      <c r="AX22" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY22" s="24" t="n"/>
-      <c r="AZ22" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA22" s="24" t="inlineStr">
-        <is>
-          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
-        </is>
-      </c>
-      <c r="BB22" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC22" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD22" s="24" t="inlineStr">
-        <is>
-          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
-        </is>
-      </c>
-      <c r="BE22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF22" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG22" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH22" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T04:07:52.173653Z</t>
-        </is>
-      </c>
-      <c r="BI22" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ22" s="25" t="n"/>
-      <c r="BK22" s="26" t="n">
-        <v>138</v>
-      </c>
-      <c r="BL22" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BM22" s="28" t="n">
-        <v>0.420168</v>
-      </c>
-      <c r="BN22" s="28" t="n"/>
-      <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BR22" s="28" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BS22" s="28" t="n"/>
-      <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
-      <c r="BV22" s="29" t="n"/>
-      <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
-      <c r="BZ22" s="24" t="n"/>
-      <c r="CA22" s="31" t="n"/>
-      <c r="CB22" s="24" t="n"/>
-      <c r="CC22" s="24" t="n"/>
-      <c r="CD22" s="24" t="n"/>
-      <c r="CE22" s="24" t="n"/>
-      <c r="CF22" s="24" t="n"/>
-      <c r="CG22" s="24" t="n"/>
-      <c r="CH22" s="24" t="n"/>
-      <c r="CI22" s="24" t="n"/>
-      <c r="CJ22" s="24" t="n"/>
-      <c r="CK22" s="24" t="n"/>
-      <c r="CL22" s="24" t="n"/>
-      <c r="CM22" s="24" t="n"/>
-      <c r="CN22" s="24" t="n"/>
-      <c r="CO22" s="24" t="n"/>
-      <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="n"/>
-      <c r="CS22" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>01ca169d9c424db6</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T04:07:53.607771Z</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>74944</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>PuckChamp</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>FTS</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="M23" s="27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="N23" s="28" t="n">
-        <v>0.390625</v>
-      </c>
-      <c r="O23" s="28" t="n">
-        <v>0.533843</v>
-      </c>
-      <c r="P23" s="28" t="n"/>
-      <c r="Q23" s="28" t="n">
-        <v>0.143218</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>92</v>
-      </c>
-      <c r="S23" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W23" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA23" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB23" s="28" t="n">
-        <v>0.009375</v>
-      </c>
-      <c r="AC23" s="30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T18:35:16.134540Z</t>
-        </is>
-      </c>
-      <c r="AE23" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-fts-pckcp-2026-08-08).</t>
-        </is>
-      </c>
-      <c r="AF23" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG23" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH23" s="24" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN23" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO23" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP23" s="24" t="inlineStr">
-        <is>
-          <t>PuckChamp</t>
-        </is>
-      </c>
-      <c r="AQ23" s="24" t="inlineStr">
-        <is>
-          <t>PuckChamp</t>
-        </is>
-      </c>
-      <c r="AR23" s="24" t="inlineStr">
-        <is>
-          <t>PuckChamp</t>
-        </is>
-      </c>
-      <c r="AS23" s="24" t="inlineStr">
-        <is>
-          <t>FTS</t>
-        </is>
-      </c>
-      <c r="AT23" s="24" t="inlineStr">
-        <is>
-          <t>FTS</t>
-        </is>
-      </c>
-      <c r="AU23" s="24" t="inlineStr">
-        <is>
-          <t>FTS</t>
-        </is>
-      </c>
-      <c r="AV23" s="24" t="n"/>
-      <c r="AW23" s="24" t="n"/>
-      <c r="AX23" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY23" s="24" t="n"/>
-      <c r="AZ23" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA23" s="24" t="inlineStr">
-        <is>
-          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
-        </is>
-      </c>
-      <c r="BB23" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC23" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD23" s="24" t="inlineStr">
-        <is>
-          <t>0cf8a886b6f638698c8273f1686e63957340d124b26747939ba7748e5424e52f</t>
-        </is>
-      </c>
-      <c r="BE23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF23" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG23" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH23" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-08T04:07:52.761230Z</t>
-        </is>
-      </c>
-      <c r="BI23" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ23" s="25" t="n"/>
-      <c r="BK23" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="BL23" s="27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BM23" s="28" t="n">
-        <v>0.390625</v>
-      </c>
-      <c r="BN23" s="28" t="n"/>
-      <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BR23" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BS23" s="28" t="n"/>
-      <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
-      <c r="BV23" s="29" t="n"/>
-      <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
-      <c r="BZ23" s="24" t="n"/>
-      <c r="CA23" s="31" t="n"/>
-      <c r="CB23" s="24" t="n"/>
-      <c r="CC23" s="24" t="n"/>
-      <c r="CD23" s="24" t="n"/>
-      <c r="CE23" s="24" t="n"/>
-      <c r="CF23" s="24" t="n"/>
-      <c r="CG23" s="24" t="n"/>
-      <c r="CH23" s="24" t="n"/>
-      <c r="CI23" s="24" t="n"/>
-      <c r="CJ23" s="24" t="n"/>
-      <c r="CK23" s="24" t="n"/>
-      <c r="CL23" s="24" t="n"/>
-      <c r="CM23" s="24" t="n"/>
-      <c r="CN23" s="24" t="n"/>
-      <c r="CO23" s="24" t="n"/>
-      <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="n"/>
-      <c r="CS23" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>9b6f24dfab3648db</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T05:41:14.399564Z</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>76395</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>Power Rangers</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L24" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="M24" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N24" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="O24" s="28" t="n">
-        <v>0.617196</v>
-      </c>
-      <c r="P24" s="28" t="n"/>
-      <c r="Q24" s="28" t="n">
-        <v>0.166746</v>
-      </c>
-      <c r="R24" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S24" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T24" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U24" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="AA24" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AB24" s="28" t="n">
-        <v>-0.00045</v>
-      </c>
-      <c r="AC24" s="30" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T16:33:35.786710Z</t>
-        </is>
-      </c>
-      <c r="AE24" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-pr-mouz-2026-08-10).</t>
-        </is>
-      </c>
-      <c r="AF24" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG24" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH24" s="24" t="n"/>
-      <c r="AI24" s="31" t="n"/>
-      <c r="AJ24" s="31" t="n"/>
-      <c r="AK24" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN24" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO24" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP24" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ</t>
-        </is>
-      </c>
-      <c r="AQ24" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ</t>
-        </is>
-      </c>
-      <c r="AR24" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ</t>
-        </is>
-      </c>
-      <c r="AS24" s="24" t="inlineStr">
-        <is>
-          <t>Power Rangers</t>
-        </is>
-      </c>
-      <c r="AT24" s="24" t="inlineStr">
-        <is>
-          <t>Power Rangers</t>
-        </is>
-      </c>
-      <c r="AU24" s="24" t="inlineStr">
-        <is>
-          <t>Power Rangers</t>
-        </is>
-      </c>
-      <c r="AV24" s="24" t="n"/>
-      <c r="AW24" s="24" t="n"/>
-      <c r="AX24" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY24" s="24" t="n"/>
-      <c r="AZ24" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA24" s="24" t="inlineStr">
-        <is>
-          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
-        </is>
-      </c>
-      <c r="BB24" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC24" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD24" s="24" t="inlineStr">
-        <is>
-          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
-        </is>
-      </c>
-      <c r="BE24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF24" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG24" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH24" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T05:41:11.396742Z</t>
-        </is>
-      </c>
-      <c r="BI24" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ24" s="25" t="n"/>
-      <c r="BK24" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="BL24" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BM24" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="BN24" s="28" t="n"/>
-      <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BR24" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BS24" s="28" t="n"/>
-      <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
-      <c r="BV24" s="29" t="n"/>
-      <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
-      <c r="BZ24" s="24" t="n"/>
-      <c r="CA24" s="31" t="n"/>
-      <c r="CB24" s="24" t="n"/>
-      <c r="CC24" s="24" t="n"/>
-      <c r="CD24" s="24" t="n"/>
-      <c r="CE24" s="24" t="n"/>
-      <c r="CF24" s="24" t="n"/>
-      <c r="CG24" s="24" t="n"/>
-      <c r="CH24" s="24" t="n"/>
-      <c r="CI24" s="24" t="n"/>
-      <c r="CJ24" s="24" t="n"/>
-      <c r="CK24" s="24" t="n"/>
-      <c r="CL24" s="24" t="n"/>
-      <c r="CM24" s="24" t="n"/>
-      <c r="CN24" s="24" t="n"/>
-      <c r="CO24" s="24" t="n"/>
-      <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="n"/>
-      <c r="CR24" s="24" t="n"/>
-      <c r="CS24" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>60856079a65f46ee</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T05:41:14.399564Z</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>76396</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="M25" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O25" s="28" t="n">
-        <v>0.5843469999999999</v>
-      </c>
-      <c r="P25" s="28" t="n"/>
-      <c r="Q25" s="28" t="n">
-        <v>0.08434700000000001</v>
-      </c>
-      <c r="R25" s="26" t="n">
-        <v>62</v>
-      </c>
-      <c r="S25" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T25" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U25" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA25" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB25" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="30" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AD25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-11T13:09:06.403801Z</t>
-        </is>
-      </c>
-      <c r="AE25" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-dota2-yes-lvlup-2026-08-10).</t>
-        </is>
-      </c>
-      <c r="AF25" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG25" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH25" s="24" t="n"/>
-      <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
-      <c r="AK25" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN25" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO25" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP25" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AQ25" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AR25" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AS25" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AT25" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AU25" s="24" t="inlineStr">
-        <is>
-          <t>Yellow Submarine</t>
-        </is>
-      </c>
-      <c r="AV25" s="24" t="n"/>
-      <c r="AW25" s="24" t="n"/>
-      <c r="AX25" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY25" s="24" t="n"/>
-      <c r="AZ25" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA25" s="24" t="inlineStr">
-        <is>
-          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
-        </is>
-      </c>
-      <c r="BB25" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC25" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD25" s="24" t="inlineStr">
-        <is>
-          <t>2e4ae6cde129603fa72e772e36ee857b52e2bf4f4d2d82d428622477e46d2626</t>
-        </is>
-      </c>
-      <c r="BE25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF25" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG25" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH25" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-10T05:41:13.718619Z</t>
-        </is>
-      </c>
-      <c r="BI25" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ25" s="25" t="n"/>
-      <c r="BK25" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL25" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM25" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN25" s="28" t="n"/>
-      <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR25" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BS25" s="28" t="n"/>
-      <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
-      <c r="BV25" s="29" t="n"/>
-      <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
-      <c r="BZ25" s="24" t="n"/>
-      <c r="CA25" s="31" t="n"/>
-      <c r="CB25" s="24" t="n"/>
-      <c r="CC25" s="24" t="n"/>
-      <c r="CD25" s="24" t="n"/>
-      <c r="CE25" s="24" t="n"/>
-      <c r="CF25" s="24" t="n"/>
-      <c r="CG25" s="24" t="n"/>
-      <c r="CH25" s="24" t="n"/>
-      <c r="CI25" s="24" t="n"/>
-      <c r="CJ25" s="24" t="n"/>
-      <c r="CK25" s="24" t="n"/>
-      <c r="CL25" s="24" t="n"/>
-      <c r="CM25" s="24" t="n"/>
-      <c r="CN25" s="24" t="n"/>
-      <c r="CO25" s="24" t="n"/>
-      <c r="CP25" s="24" t="n"/>
-      <c r="CQ25" s="24" t="n"/>
-      <c r="CR25" s="24" t="n"/>
-      <c r="CS25" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>be73ecddea644b15</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-12T08:22:28.832657Z</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-12T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>79381</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="M26" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N26" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="O26" s="28" t="n">
-        <v>0.5450159999999999</v>
-      </c>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n">
-        <v>0.094566</v>
-      </c>
-      <c r="R26" s="26" t="n">
-        <v>67</v>
-      </c>
-      <c r="S26" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W26" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="AA26" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AB26" s="28" t="n">
-        <v>-0.00045</v>
-      </c>
-      <c r="AC26" s="30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-12T14:33:48.625425Z</t>
-        </is>
-      </c>
-      <c r="AE26" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lvlup-re-2026-08-12).</t>
-        </is>
-      </c>
-      <c r="AF26" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG26" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH26" s="24" t="n"/>
-      <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
-      <c r="AK26" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM26" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN26" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO26" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP26" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AQ26" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AR26" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AS26" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AT26" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AU26" s="24" t="inlineStr">
-        <is>
-          <t>Level UP</t>
-        </is>
-      </c>
-      <c r="AV26" s="24" t="n"/>
-      <c r="AW26" s="24" t="n"/>
-      <c r="AX26" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY26" s="24" t="n"/>
-      <c r="AZ26" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA26" s="24" t="inlineStr">
-        <is>
-          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
-        </is>
-      </c>
-      <c r="BB26" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD26" s="24" t="inlineStr">
-        <is>
-          <t>4806051748ca0e0e71f7a78cdec3088c19d0b8147cff09cd9e9a8b19e8dc6791</t>
-        </is>
-      </c>
-      <c r="BE26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF26" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG26" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH26" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-12T08:22:23.388322Z</t>
-        </is>
-      </c>
-      <c r="BI26" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ26" s="25" t="n"/>
-      <c r="BK26" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="BL26" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BM26" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="BN26" s="28" t="n"/>
-      <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BR26" s="28" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BS26" s="28" t="n"/>
-      <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
-      <c r="BV26" s="29" t="n"/>
-      <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
-      <c r="BZ26" s="24" t="n"/>
-      <c r="CA26" s="31" t="n"/>
-      <c r="CB26" s="24" t="n"/>
-      <c r="CC26" s="24" t="n"/>
-      <c r="CD26" s="24" t="n"/>
-      <c r="CE26" s="24" t="n"/>
-      <c r="CF26" s="24" t="n"/>
-      <c r="CG26" s="24" t="n"/>
-      <c r="CH26" s="24" t="n"/>
-      <c r="CI26" s="24" t="n"/>
-      <c r="CJ26" s="24" t="n"/>
-      <c r="CK26" s="24" t="n"/>
-      <c r="CL26" s="24" t="n"/>
-      <c r="CM26" s="24" t="n"/>
-      <c r="CN26" s="24" t="n"/>
-      <c r="CO26" s="24" t="n"/>
-      <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="n"/>
-      <c r="CR26" s="24" t="n"/>
-      <c r="CS26" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>faa4178a0b9f43fa</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-12T19:34:36.268320Z</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-13T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>77167</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>Team Spirit</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="M27" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="N27" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="O27" s="28" t="n">
-        <v>0.738453</v>
-      </c>
-      <c r="P27" s="28" t="n"/>
-      <c r="Q27" s="28" t="n">
-        <v>0.038753</v>
-      </c>
-      <c r="R27" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U27" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
-      <c r="AE27" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-ts-xtreme-2026-08-13).</t>
-        </is>
-      </c>
-      <c r="AF27" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG27" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH27" s="24" t="n"/>
-      <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
-      <c r="AK27" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL27" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM27" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN27" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO27" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP27" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AQ27" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AR27" s="24" t="inlineStr">
-        <is>
-          <t>Xtreme Gaming</t>
-        </is>
-      </c>
-      <c r="AS27" s="24" t="inlineStr">
-        <is>
-          <t>Team Spirit</t>
-        </is>
-      </c>
-      <c r="AT27" s="24" t="inlineStr">
-        <is>
-          <t>Team Spirit</t>
-        </is>
-      </c>
-      <c r="AU27" s="24" t="inlineStr">
-        <is>
-          <t>Team Spirit</t>
-        </is>
-      </c>
-      <c r="AV27" s="24" t="n"/>
-      <c r="AW27" s="24" t="n"/>
-      <c r="AX27" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY27" s="24" t="n"/>
-      <c r="AZ27" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA27" s="24" t="inlineStr">
-        <is>
-          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
-        </is>
-      </c>
-      <c r="BB27" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BD27" s="24" t="inlineStr">
-        <is>
-          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
-        </is>
-      </c>
-      <c r="BE27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF27" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG27" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="BH27" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-12T19:34:35.104443Z</t>
-        </is>
-      </c>
-      <c r="BI27" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ27" s="25" t="n"/>
-      <c r="BK27" s="26" t="n">
-        <v>-233</v>
-      </c>
-      <c r="BL27" s="27" t="n">
-        <v>1.429185</v>
-      </c>
-      <c r="BM27" s="28" t="n">
-        <v>0.6997</v>
-      </c>
-      <c r="BN27" s="28" t="n"/>
-      <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
-      <c r="BS27" s="28" t="n"/>
-      <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
-      <c r="BV27" s="29" t="n"/>
-      <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
-      <c r="BZ27" s="24" t="n"/>
-      <c r="CA27" s="31" t="n"/>
-      <c r="CB27" s="24" t="n"/>
-      <c r="CC27" s="24" t="n"/>
-      <c r="CD27" s="24" t="n"/>
-      <c r="CE27" s="24" t="n"/>
-      <c r="CF27" s="24" t="n"/>
-      <c r="CG27" s="24" t="n"/>
-      <c r="CH27" s="24" t="n"/>
-      <c r="CI27" s="24" t="n"/>
-      <c r="CJ27" s="24" t="n"/>
-      <c r="CK27" s="24" t="n"/>
-      <c r="CL27" s="24" t="n"/>
-      <c r="CM27" s="24" t="n"/>
-      <c r="CN27" s="24" t="n"/>
-      <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="n"/>
-      <c r="CQ27" s="24" t="n"/>
-      <c r="CR27" s="24" t="n"/>
-      <c r="CS27" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
